--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R410e667072644adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R822f83d0b2594491"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -128,9 +128,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -143,12 +143,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -273,7 +319,7 @@
         <x:v>主续订单</x:v>
       </x:c>
       <x:c r="H1" s="8" t="str">
-        <x:v>总融金额</x:v>
+        <x:v>债权金额</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
         <x:v>逾期天数</x:v>

--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R822f83d0b2594491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R8086bb5bedfb42c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -471,9 +471,48 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="10"/>
-      <x:c r="D5" s="10"/>
-      <x:c r="H5" s="11"/>
+      <x:c r="A5" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>重复导入：该订单已在批次DR202606080003（创新租赁旧合同批次00）导入落库；同一批资产多次导入时，以首次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>请到首次导入批次DR202606080003查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="10"/>
@@ -5450,6 +5489,50 @@
       <x:c r="D1000" s="10"/>
       <x:c r="H1000" s="11"/>
     </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="B1001" t="str">
+        <x:v>DR202606100001</x:v>
+      </x:c>
+      <x:c r="C1001" t="str">
+        <x:v>创新租赁旧合同批次01</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>26012915050167612331</x:v>
+      </x:c>
+      <x:c r="E1001" t="str">
+        <x:v>周强</x:v>
+      </x:c>
+      <x:c r="F1001" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="G1001" t="str">
+        <x:v>主订单</x:v>
+      </x:c>
+      <x:c r="H1001" t="n">
+        <x:v>8650</x:v>
+      </x:c>
+      <x:c r="I1001" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J1001" t="str">
+        <x:v>阻断失败</x:v>
+      </x:c>
+      <x:c r="K1001" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L1001" t="str">
+        <x:v>同一批资产已在批次 DR202606080003 导入落库，以第一次导入数据为准，本批次不能重复导入或自动覆盖。</x:v>
+      </x:c>
+      <x:c r="M1001" t="str">
+        <x:v>请到首次导入批次查看该订单；如需更正，按原批次处理或走批量补传/更正流程。</x:v>
+      </x:c>
+      <x:c r="N1001" t="str">
+        <x:v>2026-06-10 20:15:32</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R8086bb5bedfb42c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rd7a594442a764abb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Re5f6e7f229ed4836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R2ca5f2b09b9042ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="R809f876134d241ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R85d45ad1527c4435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R9678838870e94822"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="Rc72602e2cbf545a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -331,8 +331,7 @@
     <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -379,9 +378,6 @@
         <x:v>是否阻断导入</x:v>
       </x:c>
       <x:c r="O1" s="7" t="str">
-        <x:v>处理建议</x:v>
-      </x:c>
-      <x:c r="P1" s="7" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
@@ -423,15 +419,12 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>字段校验通过，已生成待委外案件</x:v>
+        <x:v>字段校验通过，案件已生成并生效，已进入待委外队列</x:v>
       </x:c>
       <x:c r="N2" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="O2" s="10" t="str">
-        <x:v>无需处理</x:v>
-      </x:c>
-      <x:c r="P2" s="12" t="str">
+      <x:c r="O2" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -476,10 +469,7 @@
       <x:c r="N3" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O3" s="10" t="str">
-        <x:v>补充债权金额后重新导入</x:v>
-      </x:c>
-      <x:c r="P3" s="12" t="str">
+      <x:c r="O3" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -526,10 +516,7 @@
       <x:c r="N4" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O4" s="10" t="str">
-        <x:v>修正身份证号后重新导入</x:v>
-      </x:c>
-      <x:c r="P4" s="12" t="str">
+      <x:c r="O4" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -576,10 +563,7 @@
       <x:c r="N5" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O5" s="10" t="str">
-        <x:v>修正为大于等于0的金额后重新导入</x:v>
-      </x:c>
-      <x:c r="P5" s="12" t="str">
+      <x:c r="O5" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -626,10 +610,7 @@
       <x:c r="N6" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O6" s="10" t="str">
-        <x:v>按模板枚举填写后重新导入</x:v>
-      </x:c>
-      <x:c r="P6" s="12" t="str">
+      <x:c r="O6" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -676,10 +657,7 @@
       <x:c r="N7" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O7" s="10" t="str">
-        <x:v>补充主订单或修正父订单编号后重新导入</x:v>
-      </x:c>
-      <x:c r="P7" s="12" t="str">
+      <x:c r="O7" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -726,10 +704,7 @@
       <x:c r="N8" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O8" s="10" t="str">
-        <x:v>核对历史批次，如需修正请走后续更正流程</x:v>
-      </x:c>
-      <x:c r="P8" s="12" t="str">
+      <x:c r="O8" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -776,10 +751,7 @@
       <x:c r="N9" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O9" s="10" t="str">
-        <x:v>确认订单状态，剔除后重新导入</x:v>
-      </x:c>
-      <x:c r="P9" s="12" t="str">
+      <x:c r="O9" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -826,10 +798,7 @@
       <x:c r="N10" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O10" s="10" t="str">
-        <x:v>使用系统下载的最新模板重新填写</x:v>
-      </x:c>
-      <x:c r="P10" s="12" t="str">
+      <x:c r="O10" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -876,10 +845,7 @@
       <x:c r="N11" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="O11" s="10" t="str">
-        <x:v>暂不重复导入，待系统修复后重试</x:v>
-      </x:c>
-      <x:c r="P11" s="12" t="str">
+      <x:c r="O11" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
@@ -896,7 +862,6 @@
     <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -912,9 +877,6 @@
       <x:c r="D1" s="17" t="str">
         <x:v>示例</x:v>
       </x:c>
-      <x:c r="E1" s="17" t="str">
-        <x:v>处理口径</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
@@ -929,9 +891,6 @@
       <x:c r="D2" s="10" t="str">
         <x:v>缺少违约日列</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>使用系统下载模板重新填写后导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
@@ -946,9 +905,6 @@
       <x:c r="D3" s="10" t="str">
         <x:v>订单编号、姓名、身份证号、债权金额为空</x:v>
       </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>补齐字段后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
@@ -963,9 +919,6 @@
       <x:c r="D4" s="10" t="str">
         <x:v>身份证号不足18位</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="str">
-        <x:v>修正字段格式后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
@@ -980,9 +933,6 @@
       <x:c r="D5" s="10" t="str">
         <x:v>债权金额=-5999</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="str">
-        <x:v>修正金额后重新导入</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
@@ -997,9 +947,6 @@
       <x:c r="D6" s="10" t="str">
         <x:v>性别=未知</x:v>
       </x:c>
-      <x:c r="E6" s="10" t="str">
-        <x:v>按模板枚举填写</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
@@ -1014,9 +961,6 @@
       <x:c r="D7" s="10" t="str">
         <x:v>续租订单缺少父订单编号</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="str">
-        <x:v>补充主订单或修正父订单编号</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
@@ -1031,9 +975,6 @@
       <x:c r="D8" s="10" t="str">
         <x:v>已在DR202606100001导入</x:v>
       </x:c>
-      <x:c r="E8" s="10" t="str">
-        <x:v>以首次导入批次为准，本次跳过</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
@@ -1048,9 +989,6 @@
       <x:c r="D9" s="10" t="str">
         <x:v>已结清订单</x:v>
       </x:c>
-      <x:c r="E9" s="10" t="str">
-        <x:v>剔除或确认状态后重导</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
@@ -1064,9 +1002,6 @@
       </x:c>
       <x:c r="D10" s="10" t="str">
         <x:v>数据库写入失败</x:v>
-      </x:c>
-      <x:c r="E10" s="10" t="str">
-        <x:v>联系研发排查后重试</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1143,31 +1078,42 @@
         <x:v>案件生成</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>字段、金额、主续关系、订单状态校验通过后生成案件。</x:v>
+        <x:v>字段校验通过即可生成案件，案件立即生效并进入待委外队列。</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>材料齐套校验放二期。</x:v>
+        <x:v>二期材料导入不影响一期案件生效口径。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>重复订单</x:v>
+        <x:v>导出限制</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>历史批次已导入的订单本次跳过，并提示已存在批次号。</x:v>
+        <x:v>一期导入案件可进行后续法诉流程，但不支持导出要素表和导出法诉材料。</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>二期再评估覆盖和材料补充规则。</x:v>
+        <x:v>二期材料导入完成后再评估导出能力。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
+        <x:v>重复订单</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>历史批次已导入的订单本次跳过，并提示已存在批次号。</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>二期再评估覆盖和材料补充规则。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
         <x:v>材料状态</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>一期不展示材料待处理、待补材料、未匹配材料池。</x:v>
       </x:c>
-      <x:c r="C8" s="10" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>二期通过材料导入和处理详情承接。</x:v>
       </x:c>
     </x:row>

--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R85d45ad1527c4435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R9678838870e94822"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="Rc72602e2cbf545a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R6cb52f6d42e9491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R80f6f482cf404bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="R276bd5ecff8d4db9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,23 +15,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd hh:mm:ss"/>
-  </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF243447"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
       <x:b/>
-      <x:sz val="11"/>
+      <x:sz val="10"/>
       <x:color rgb="FF1F2937"/>
-      <x:name val="Carlito"/>
+      <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,7 +41,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F6FC"/>
+        <x:fgColor rgb="FFE9EDF2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -48,78 +54,120 @@
     <x:border/>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFD9E2EC"/>
+        <x:color rgb="FFD8E0E8"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFD9E2EC"/>
+        <x:color rgb="FFD8E0E8"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFD9E2EC"/>
+        <x:color rgb="FFD8E0E8"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFD9E2EC"/>
+        <x:color rgb="FFD8E0E8"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE5E7EB"/>
+        <x:color rgb="FFC7D0DA"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFE5E7EB"/>
+        <x:color rgb="FFC7D0DA"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE5E7EB"/>
+        <x:color rgb="FFC7D0DA"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE5E7EB"/>
+        <x:color rgb="FFC7D0DA"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportResultTable" displayName="ImportResultTable" ref="A1:N11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:N11"/>
+  <x:tableColumns count="14">
+    <x:tableColumn id="1" name="导入批次号"/>
+    <x:tableColumn id="2" name="批次名称"/>
+    <x:tableColumn id="3" name="外部资产方"/>
+    <x:tableColumn id="4" name="业务类型"/>
+    <x:tableColumn id="5" name="订单编号"/>
+    <x:tableColumn id="6" name="客户姓名"/>
+    <x:tableColumn id="7" name="身份证号"/>
+    <x:tableColumn id="8" name="导入结果"/>
+    <x:tableColumn id="9" name="失败分类"/>
+    <x:tableColumn id="10" name="失败字段"/>
+    <x:tableColumn id="11" name="字段值"/>
+    <x:tableColumn id="12" name="失败原因"/>
+    <x:tableColumn id="13" name="是否阻断导入"/>
+    <x:tableColumn id="14" name="导入时间"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FailureCategoryTable" displayName="FailureCategoryTable" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D11"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="分类/规则"/>
+    <x:tableColumn id="2" name="触发场景"/>
+    <x:tableColumn id="3" name="是否阻断"/>
+    <x:tableColumn id="4" name="示例"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PhaseOneScopeTable" displayName="PhaseOneScopeTable" ref="A1:C10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:C10"/>
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="口径项"/>
+    <x:tableColumn id="2" name="一期说明"/>
+    <x:tableColumn id="3" name="二期边界"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -318,70 +366,66 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="62" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="7" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="8" t="str">
         <x:v>导入批次号</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>批次名称</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>外部资产方</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>业务类型</x:v>
       </x:c>
-      <x:c r="E1" s="7" t="str">
-        <x:v>行号</x:v>
-      </x:c>
-      <x:c r="F1" s="7" t="str">
+      <x:c r="E1" s="8" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="G1" s="7" t="str">
+      <x:c r="F1" s="8" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="H1" s="7" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="I1" s="7" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>导入结果</x:v>
       </x:c>
-      <x:c r="J1" s="7" t="str">
+      <x:c r="I1" s="8" t="str">
         <x:v>失败分类</x:v>
       </x:c>
-      <x:c r="K1" s="7" t="str">
+      <x:c r="J1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="L1" s="7" t="str">
+      <x:c r="K1" s="8" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="M1" s="7" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>失败原因</x:v>
       </x:c>
-      <x:c r="N1" s="7" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="O1" s="7" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -394,41 +438,38 @@
       <x:c r="D2" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="n">
-        <x:v>2</x:v>
+      <x:c r="E2" s="10" t="str">
+        <x:v>‌26012915050167612327</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>‌26012915050167612327</x:v>
+        <x:v>张三</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>张三</x:v>
+        <x:v>‌420106199201018888</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>‌420106199201018888</x:v>
-      </x:c>
-      <x:c r="I2" s="11" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="J2" s="11" t="str">
+      <x:c r="I2" s="10" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="L2" s="10" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
         <x:v>字段校验通过，案件已生成并生效，已进入待委外队列</x:v>
       </x:c>
+      <x:c r="M2" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
       <x:c r="N2" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="O2" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -441,39 +482,36 @@
       <x:c r="D3" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E3" s="11" t="n">
-        <x:v>3</x:v>
+      <x:c r="E3" s="10" t="str">
+        <x:v>‌26012915050167612328</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>‌26012915050167612328</x:v>
+        <x:v>李明</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>李明</x:v>
+        <x:v>‌420106199201019999</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>‌420106199201019999</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J3" s="11" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="K3" s="10" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="L3" s="10" t="str"/>
-      <x:c r="M3" s="10" t="str">
-        <x:v>债权金额为导入规则必填字段，当前为空</x:v>
+      <x:c r="K3" s="10"/>
+      <x:c r="L3" s="10" t="str">
+        <x:v>债权金额为必填字段，当前为空</x:v>
+      </x:c>
+      <x:c r="M3" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N3" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O3" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -486,41 +524,38 @@
       <x:c r="D4" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="n">
-        <x:v>4</x:v>
+      <x:c r="E4" s="10" t="str">
+        <x:v>‌26012915050167612329</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>‌26012915050167612329</x:v>
+        <x:v>王磊</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>王磊</x:v>
+        <x:v>‌42010619920101</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
+        <x:v>导入失败</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>字段格式错误</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
+        <x:v>身份证号</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
         <x:v>‌42010619920101</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="str">
-        <x:v>导入失败</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>字段格式错误</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str">
-        <x:v>身份证号</x:v>
-      </x:c>
       <x:c r="L4" s="10" t="str">
-        <x:v>‌42010619920101</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>身份证号格式不正确，应为18位身份证号码</x:v>
+        <x:v>身份证号字段格式错误</x:v>
+      </x:c>
+      <x:c r="M4" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N4" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O4" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -533,41 +568,38 @@
       <x:c r="D5" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="n">
-        <x:v>5</x:v>
+      <x:c r="E5" s="10" t="str">
+        <x:v>‌26012915050167612330</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>‌26012915050167612330</x:v>
+        <x:v>黄丽</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>黄丽</x:v>
+        <x:v>‌420106199201017777</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>‌420106199201017777</x:v>
-      </x:c>
-      <x:c r="I5" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>金额异常</x:v>
       </x:c>
+      <x:c r="J5" s="10" t="str">
+        <x:v>债权金额</x:v>
+      </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>债权金额</x:v>
+        <x:v>-5999.00</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str">
-        <x:v>-5999.00</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>金额需为数字且不可为负值</x:v>
+        <x:v>债权金额异常</x:v>
+      </x:c>
+      <x:c r="M5" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N5" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O5" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -580,41 +612,38 @@
       <x:c r="D6" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>6</x:v>
+      <x:c r="E6" s="10" t="str">
+        <x:v>‌26012915050167612331</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>‌26012915050167612331</x:v>
+        <x:v>周强</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>周强</x:v>
+        <x:v>‌420106199201016666</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>‌420106199201016666</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>枚举值错误</x:v>
+      <x:c r="I6" s="10" t="str">
+        <x:v>字段格式错误</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="str">
+        <x:v>性别</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>性别</x:v>
+        <x:v>未知</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str">
-        <x:v>未知</x:v>
-      </x:c>
-      <x:c r="M6" s="10" t="str">
-        <x:v>字段值不在系统允许枚举范围内</x:v>
+        <x:v>性别字段格式错误</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N6" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O6" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -627,41 +656,38 @@
       <x:c r="D7" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="n">
-        <x:v>7</x:v>
+      <x:c r="E7" s="10" t="str">
+        <x:v>‌26012915050167612332</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>‌26012915050167612332</x:v>
+        <x:v>赵倩</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>赵倩</x:v>
+        <x:v>‌420106199201015555</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>‌420106199201015555</x:v>
-      </x:c>
-      <x:c r="I7" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
+      <x:c r="J7" s="10" t="str">
+        <x:v>父订单编号</x:v>
+      </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>父订单编号</x:v>
+        <x:v>‌26012915050167610001</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>‌26012915050167610001</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
         <x:v>父订单编号不存在，且本批次未导入对应主订单</x:v>
       </x:c>
+      <x:c r="M7" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="N7" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O7" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -674,41 +700,38 @@
       <x:c r="D8" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>8</x:v>
+      <x:c r="E8" s="10" t="str">
+        <x:v>‌26012915050167612336</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>‌26012915050167612333</x:v>
+        <x:v>孙悦</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>陈晨</x:v>
+        <x:v>‌420106199201010001</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>‌420106199201014444</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>重复跳过</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str">
-        <x:v>重复订单</x:v>
+        <x:v>导入失败</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str">
+        <x:v>主续关系异常</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="str">
+        <x:v>身份证号</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>订单编号</x:v>
+        <x:v>‌420106199201010001</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>‌26012915050167612333</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>该订单已在批次DR202606100001导入，本次不重复落库</x:v>
+        <x:v>父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N8" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O8" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -721,41 +744,36 @@
       <x:c r="D9" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>9</x:v>
+      <x:c r="E9" s="10" t="str">
+        <x:v>‌26012915050167612337</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>‌26012915050167612334</x:v>
+        <x:v>郑楠</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>刘洋</x:v>
+        <x:v>‌420106199201010002</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>‌420106199201013333</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="str">
-        <x:v>订单状态不允许</x:v>
-      </x:c>
-      <x:c r="K9" s="10" t="str">
-        <x:v>订单状态</x:v>
-      </x:c>
+      <x:c r="I9" s="10" t="str">
+        <x:v>基础必填缺失</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="str">
+        <x:v>违约日</x:v>
+      </x:c>
+      <x:c r="K9" s="10"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>已结清</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>已结清订单不允许进入法诉导入</x:v>
+        <x:v>续租订单违约日不能为空，请补充后重新上传。</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N9" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O9" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -768,41 +786,38 @@
       <x:c r="D10" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>-</x:v>
+      <x:c r="E10" s="10" t="str">
+        <x:v>‌26012915050167612333</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>-</x:v>
+        <x:v>陈晨</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>-</x:v>
+        <x:v>‌420106199201014444</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J10" s="11" t="str">
-        <x:v>模板格式错误</x:v>
+      <x:c r="I10" s="10" t="str">
+        <x:v>重复订单</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="str">
+        <x:v>订单编号</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>模板列头</x:v>
+        <x:v>‌26012915050167612333</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>缺少违约日</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>模板缺少导入规则必填列：违约日</x:v>
+        <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N10" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O10" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="10" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
@@ -815,42 +830,42 @@
       <x:c r="D11" s="10" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="n">
-        <x:v>10</x:v>
+      <x:c r="E11" s="10" t="str">
+        <x:v>‌26012915050167612334</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>‌26012915050167612335</x:v>
+        <x:v>刘洋</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>许敏</x:v>
+        <x:v>‌420106199201013333</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>‌420106199201012222</x:v>
-      </x:c>
-      <x:c r="I11" s="11" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J11" s="11" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>系统异常</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="str">
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>落库失败，请联系研发排查日志</x:v>
+        <x:v>系统异常</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="N11" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="O11" s="12" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re20d5484dc2e483e"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -858,154 +873,171 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="17" t="str">
-        <x:v>失败分类</x:v>
-      </x:c>
-      <x:c r="B1" s="17" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>分类/规则</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
         <x:v>触发场景</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>是否阻断</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>示例</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="10" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="9" t="str">
+        <x:v>文件级前置校验</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>订单编号为空、同一Excel订单编号重复、必填列缺失、重复列头、文件超过50MB、订单超过500条</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>模板中有重复订单，请修正后重新上传。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="9" t="str">
         <x:v>模板格式错误</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>文件格式不支持、缺少必填列、列头与模板不一致</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>缺少违约日列</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="10" t="str">
+      <x:c r="B3" s="9" t="str">
+        <x:v>文件格式不支持、文件无法解析、列头名称与模板不一致</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>缺少必填列：违约日</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="9" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>导入规则配置为必填的字段为空</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="str">
-        <x:v>订单编号、姓名、身份证号、债权金额为空</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="10" t="str">
+      <x:c r="B4" s="9" t="str">
+        <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>续租订单违约日为空</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="9" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>身份证号、手机号、日期等格式不符合规则</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>身份证号不足18位</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="10" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>身份证号字段格式错误</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="9" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>金额非数字、负数，或金额关系不合法</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="str">
-        <x:v>债权金额=-5999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="10" t="str">
-        <x:v>枚举值错误</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>字段值不在系统允许枚举范围内</x:v>
-      </x:c>
-      <x:c r="C6" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="str">
-        <x:v>性别=未知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="10" t="str">
+      <x:c r="C6" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>债权金额异常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="9" t="str">
+        <x:v>首错输出规则</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>同一订单命中多个字段或多类校验问题时，仅输出按优先级命中的首个失败原因</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>基础必填缺失 → 字段格式错误 → 金额异常 → 主续关系异常 → 重复订单 → 系统异常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="9" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>父订单编号不存在、父子客户信息不一致</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="str">
-        <x:v>续租订单缺少父订单编号</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="10" t="str">
+      <x:c r="B8" s="9" t="str">
+        <x:v>先按外部资产方+父订单编号查询系统主订单，未匹配再查本批次；均不存在或父子证件号不一致</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>未匹配到父订单，或父子订单证件号不一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="9" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>同批重复或历史批次已导入</x:v>
-      </x:c>
-      <x:c r="C8" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="str">
-        <x:v>已在DR202606100001导入</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="10" t="str">
-        <x:v>订单状态不允许</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>系统已有订单状态不允许进入法诉导入</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="str">
-        <x:v>已结清订单</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="10" t="str">
+      <x:c r="B9" s="9" t="str">
+        <x:v>同一外部资产方+订单编号已在其他批次导入，或同批次订单已流转不可覆盖</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="9" t="str">
+        <x:v>失败文案规范</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>字段格式与金额异常按统一格式输出，便于运营定位Excel列</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>字段名+字段格式错误；字段名+金额异常；系统异常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="9" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>解析、校验或落库发生技术异常</x:v>
-      </x:c>
-      <x:c r="C10" s="10" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="D10" s="10" t="str">
-        <x:v>数据库写入失败</x:v>
+      <x:c r="B11" s="9" t="str">
+        <x:v>单笔订单解析、校验或落库发生技术异常；任务级异常不进入订单明细</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>系统异常</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd47e9415b70c4c61"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -1013,111 +1045,125 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="17" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="8" t="str">
         <x:v>口径项</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>一期说明</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>二期边界</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="10" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="9" t="str">
         <x:v>导入范围</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>一期只做资产明细Excel导入。</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="B2" s="9" t="str">
+        <x:v>一期只做资产明细Excel导入，不做材料导入。</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
         <x:v>材料导入放二期。</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="10" t="str">
-        <x:v>草稿功能</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>一期不做保存草稿，管理列表不展示草稿状态。</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>如后续需要，可单独评估草稿。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="10" t="str">
-        <x:v>批次状态</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>导入中、导入完成、导入失败。</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="str">
-        <x:v>二期再增加材料处理相关状态。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="10" t="str">
-        <x:v>导入后动作</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>点击导入后自动下载导入结果明细。</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>提交后动作</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>点击导入后提交异步任务；处理完成弹出“导入完成”或“导入失败”，点击确定后返回案件导入管理列表。</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
         <x:v>二期再进入导入处理详情处理材料。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="10" t="str">
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="9" t="str">
+        <x:v>明细下载</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>在案件导入管理列表点击下载明细；下载批次全量订单最新结果，同一失败订单仅展示首个失败原因。</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>二期处理详情可补充更细解析。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="9" t="str">
+        <x:v>文件级前置校验</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>订单编号为空、同一Excel订单编号重复、订单超过500条、文件超过50MB、必填列缺失等均上传失败，不创建导入任务。</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>二期材料包另行增加解压和文件命名校验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="9" t="str">
         <x:v>案件生成</x:v>
       </x:c>
-      <x:c r="B6" s="10" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>字段校验通过即可生成案件，案件立即生效并进入待委外队列。</x:v>
       </x:c>
-      <x:c r="C6" s="10" t="str">
+      <x:c r="C6" s="9" t="str">
         <x:v>二期材料导入不影响一期案件生效口径。</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="10" t="str">
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="9" t="str">
+        <x:v>应还日期</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>账单应还日期取违约日；续租订单违约日必填；主订单和续租订单同批导入时主订单非必填。</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>二期仍沿用该口径。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="9" t="str">
+        <x:v>重复订单</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>跨批次重复不允许导入，并在明细中提示已存在批次号；同一Excel内重复直接上传失败。</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>二期再评估材料补充规则。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="9" t="str">
+        <x:v>统计口径</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>资产总数、导入成功、导入失败均按订单编号去重，取当前批次下订单最新有效处理结果。</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>二期材料状态另行统计。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="9" t="str">
         <x:v>导出限制</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>一期导入案件可进行后续法诉流程，但不支持导出要素表和导出法诉材料。</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>一期导入案件可进入后续法诉流程，但不支持导出要素表和导出法诉材料。</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
         <x:v>二期材料导入完成后再评估导出能力。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="10" t="str">
-        <x:v>重复订单</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>历史批次已导入的订单本次跳过，并提示已存在批次号。</x:v>
-      </x:c>
-      <x:c r="C8" s="10" t="str">
-        <x:v>二期再评估覆盖和材料补充规则。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="10" t="str">
-        <x:v>材料状态</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>一期不展示材料待处理、待补材料、未匹配材料池。</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>二期通过材料导入和处理详情承接。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc498a921607b4adc"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R6cb52f6d42e9491c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R80f6f482cf404bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="R276bd5ecff8d4db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R522657f973a24d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R840549bea69c46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一期口径说明" sheetId="3" r:id="R030133c76fc746d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -84,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -109,12 +109,6 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -123,8 +117,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportResultTable" displayName="ImportResultTable" ref="A1:N11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:N11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImportResultTable" displayName="ImportResultTable" ref="A1:N10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:N10"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -146,13 +140,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FailureCategoryTable" displayName="FailureCategoryTable" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D11"/>
-  <x:tableColumns count="4">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FailureCategoryTable" displayName="FailureCategoryTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="分类/规则"/>
     <x:tableColumn id="2" name="触发场景"/>
     <x:tableColumn id="3" name="是否阻断"/>
     <x:tableColumn id="4" name="示例"/>
+    <x:tableColumn id="5" name="提示文案"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -426,445 +421,401 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="C2" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str">
+      <x:c r="D2" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="E2" s="9" t="str">
         <x:v>‌26012915050167612327</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="F2" s="9" t="str">
         <x:v>张三</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="G2" s="9" t="str">
         <x:v>‌420106199201018888</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="H2" s="9" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="I2" s="9" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="J2" s="10" t="str">
+      <x:c r="J2" s="9" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="K2" s="10" t="str">
+      <x:c r="K2" s="9" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L2" s="10" t="str">
+      <x:c r="L2" s="9" t="str">
         <x:v>字段校验通过，案件已生成并生效，已进入待委外队列</x:v>
       </x:c>
-      <x:c r="M2" s="11" t="str">
+      <x:c r="M2" s="9" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="N2" s="11" t="str">
+      <x:c r="N2" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="10" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="str">
+      <x:c r="B3" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C3" s="10" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D3" s="10" t="str">
+      <x:c r="D3" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E3" s="10" t="str">
+      <x:c r="E3" s="9" t="str">
         <x:v>‌26012915050167612328</x:v>
       </x:c>
-      <x:c r="F3" s="10" t="str">
+      <x:c r="F3" s="9" t="str">
         <x:v>李明</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="str">
+      <x:c r="G3" s="9" t="str">
         <x:v>‌420106199201019999</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str">
+      <x:c r="H3" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I3" s="10" t="str">
+      <x:c r="I3" s="9" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="J3" s="10" t="str">
+      <x:c r="J3" s="9" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="K3" s="10"/>
-      <x:c r="L3" s="10" t="str">
+      <x:c r="K3" s="9"/>
+      <x:c r="L3" s="9" t="str">
         <x:v>债权金额为必填字段，当前为空</x:v>
       </x:c>
-      <x:c r="M3" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N3" s="11" t="str">
+      <x:c r="M3" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N3" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="10" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="str">
+      <x:c r="B4" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C4" s="10" t="str">
+      <x:c r="C4" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D4" s="10" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="str">
+      <x:c r="E4" s="9" t="str">
         <x:v>‌26012915050167612329</x:v>
       </x:c>
-      <x:c r="F4" s="10" t="str">
+      <x:c r="F4" s="9" t="str">
         <x:v>王磊</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="str">
+      <x:c r="G4" s="9" t="str">
         <x:v>‌42010619920101</x:v>
       </x:c>
-      <x:c r="H4" s="10" t="str">
+      <x:c r="H4" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="str">
+      <x:c r="I4" s="9" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="J4" s="10" t="str">
+      <x:c r="J4" s="9" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="K4" s="10" t="str">
+      <x:c r="K4" s="9" t="str">
         <x:v>‌42010619920101</x:v>
       </x:c>
-      <x:c r="L4" s="10" t="str">
+      <x:c r="L4" s="9" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-      <x:c r="M4" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N4" s="11" t="str">
+      <x:c r="M4" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N4" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="10" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>‌26012915050167612330</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>黄丽</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>‌420106199201017777</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="str">
+      <x:c r="I5" s="9" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="str">
+      <x:c r="J5" s="9" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="str">
+      <x:c r="K5" s="9" t="str">
         <x:v>-5999.00</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="str">
+      <x:c r="L5" s="9" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-      <x:c r="M5" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N5" s="11" t="str">
+      <x:c r="M5" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N5" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="10" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B6" s="10" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C6" s="10" t="str">
+      <x:c r="C6" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D6" s="10" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E6" s="10" t="str">
+      <x:c r="E6" s="9" t="str">
         <x:v>‌26012915050167612331</x:v>
       </x:c>
-      <x:c r="F6" s="10" t="str">
+      <x:c r="F6" s="9" t="str">
         <x:v>周强</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str">
+      <x:c r="G6" s="9" t="str">
         <x:v>‌420106199201016666</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str">
+      <x:c r="H6" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I6" s="10" t="str">
+      <x:c r="I6" s="9" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="J6" s="10" t="str">
+      <x:c r="J6" s="9" t="str">
         <x:v>性别</x:v>
       </x:c>
-      <x:c r="K6" s="10" t="str">
+      <x:c r="K6" s="9" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="L6" s="10" t="str">
+      <x:c r="L6" s="9" t="str">
         <x:v>性别字段格式错误</x:v>
       </x:c>
-      <x:c r="M6" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N6" s="11" t="str">
+      <x:c r="M6" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N6" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="10" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
+      <x:c r="B7" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="str">
+      <x:c r="C7" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="str">
+      <x:c r="D7" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="str">
+      <x:c r="E7" s="9" t="str">
         <x:v>‌26012915050167612332</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="str">
+      <x:c r="F7" s="9" t="str">
         <x:v>赵倩</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
+      <x:c r="G7" s="9" t="str">
         <x:v>‌420106199201015555</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="str">
+      <x:c r="H7" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="str">
+      <x:c r="I7" s="9" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="str">
+      <x:c r="J7" s="9" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="str">
+      <x:c r="K7" s="9" t="str">
         <x:v>‌26012915050167610001</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="str">
+      <x:c r="L7" s="9" t="str">
         <x:v>父订单编号不存在，且本批次未导入对应主订单</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N7" s="11" t="str">
+      <x:c r="M7" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N7" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="10" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
+      <x:c r="B8" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C8" s="10" t="str">
+      <x:c r="C8" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D8" s="10" t="str">
+      <x:c r="D8" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E8" s="10" t="str">
+      <x:c r="E8" s="9" t="str">
         <x:v>‌26012915050167612336</x:v>
       </x:c>
-      <x:c r="F8" s="10" t="str">
+      <x:c r="F8" s="9" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str">
+      <x:c r="G8" s="9" t="str">
         <x:v>‌420106199201010001</x:v>
       </x:c>
-      <x:c r="H8" s="10" t="str">
+      <x:c r="H8" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I8" s="10" t="str">
+      <x:c r="I8" s="9" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="J8" s="10" t="str">
+      <x:c r="J8" s="9" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="K8" s="10" t="str">
+      <x:c r="K8" s="9" t="str">
         <x:v>‌420106199201010001</x:v>
       </x:c>
-      <x:c r="L8" s="10" t="str">
+      <x:c r="L8" s="9" t="str">
         <x:v>父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N8" s="11" t="str">
+      <x:c r="M8" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N8" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="10" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B9" s="10" t="str">
+      <x:c r="B9" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C9" s="10" t="str">
+      <x:c r="C9" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D9" s="10" t="str">
+      <x:c r="D9" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E9" s="10" t="str">
+      <x:c r="E9" s="9" t="str">
         <x:v>‌26012915050167612337</x:v>
       </x:c>
-      <x:c r="F9" s="10" t="str">
+      <x:c r="F9" s="9" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="str">
+      <x:c r="G9" s="9" t="str">
         <x:v>‌420106199201010002</x:v>
       </x:c>
-      <x:c r="H9" s="10" t="str">
+      <x:c r="H9" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I9" s="10" t="str">
+      <x:c r="I9" s="9" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="J9" s="10" t="str">
+      <x:c r="J9" s="9" t="str">
         <x:v>违约日</x:v>
       </x:c>
-      <x:c r="K9" s="10"/>
-      <x:c r="L9" s="10" t="str">
+      <x:c r="K9" s="9"/>
+      <x:c r="L9" s="9" t="str">
         <x:v>续租订单违约日不能为空，请补充后重新上传。</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N9" s="11" t="str">
+      <x:c r="M9" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N9" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="10" t="str">
+      <x:c r="A10" s="9" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="str">
+      <x:c r="B10" s="9" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C10" s="10" t="str">
+      <x:c r="C10" s="9" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D10" s="10" t="str">
+      <x:c r="D10" s="9" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E10" s="10" t="str">
+      <x:c r="E10" s="9" t="str">
         <x:v>‌26012915050167612333</x:v>
       </x:c>
-      <x:c r="F10" s="10" t="str">
+      <x:c r="F10" s="9" t="str">
         <x:v>陈晨</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str">
+      <x:c r="G10" s="9" t="str">
         <x:v>‌420106199201014444</x:v>
       </x:c>
-      <x:c r="H10" s="10" t="str">
+      <x:c r="H10" s="9" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I10" s="10" t="str">
+      <x:c r="I10" s="9" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="J10" s="10" t="str">
+      <x:c r="J10" s="9" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="K10" s="10" t="str">
+      <x:c r="K10" s="9" t="str">
         <x:v>‌26012915050167612333</x:v>
       </x:c>
-      <x:c r="L10" s="10" t="str">
+      <x:c r="L10" s="9" t="str">
         <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N10" s="11" t="str">
-        <x:v>2026-06-12 09:20:16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="10" t="str">
-        <x:v>DR202606120003</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>创新租赁一期Excel导入批次04</x:v>
-      </x:c>
-      <x:c r="C11" s="10" t="str">
-        <x:v>创新</x:v>
-      </x:c>
-      <x:c r="D11" s="10" t="str">
-        <x:v>租赁</x:v>
-      </x:c>
-      <x:c r="E11" s="10" t="str">
-        <x:v>‌26012915050167612334</x:v>
-      </x:c>
-      <x:c r="F11" s="10" t="str">
-        <x:v>刘洋</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str">
-        <x:v>‌420106199201013333</x:v>
-      </x:c>
-      <x:c r="H11" s="10" t="str">
-        <x:v>导入失败</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="str">
-        <x:v>系统异常</x:v>
-      </x:c>
-      <x:c r="J11" s="10" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="K11" s="10" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L11" s="10" t="str">
-        <x:v>系统异常</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="N11" s="11" t="str">
+      <x:c r="M10" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N10" s="9" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re20d5484dc2e483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb92f1a0fe8574526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -874,9 +825,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -892,8 +844,11 @@
       <x:c r="D1" s="8" t="str">
         <x:v>示例</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="E1" s="8" t="str">
+        <x:v>提示文案</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="88" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>文件级前置校验</x:v>
       </x:c>
@@ -906,22 +861,33 @@
       <x:c r="D2" s="9" t="str">
         <x:v>模板中有重复订单，请修正后重新上传。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="E2" s="9" t="str">
+        <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
+重复订单：模板中有重复订单，请修正后重新上传。
+文件超过50MB：上传文件超过50MB，请压缩或拆分后重新上传。
+订单超过500条：单次导入最多支持500条订单，请拆分后重新上传。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="88" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>模板格式错误</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>文件格式不支持、文件无法解析、列头名称与模板不一致</x:v>
+        <x:v>文件无法解析、列头名称与模板不一致、缺少必填列等模板问题</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>是</x:v>
+        <x:v>上传阶段拦截</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>缺少必填列：违约日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="42" customHeight="1">
+        <x:v>整份文件上传失败，不创建任务</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
+        <x:v>文件无法解析：文件无法解析，请确认文件未损坏且格式为xlsx/xls后重新上传。
+列头不一致：模板列头【实际列名】与标准模板不一致，请下载最新模板修正后重新上传。
+缺少必填列：模板缺少必填列【列名】，请修正后重新上传。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="88" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
@@ -934,8 +900,11 @@
       <x:c r="D4" s="9" t="str">
         <x:v>续租订单违约日为空</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="E4" s="9" t="str">
+        <x:v>【字段名】不能为空</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="88" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
@@ -948,8 +917,11 @@
       <x:c r="D5" s="9" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="E5" s="9" t="str">
+        <x:v>【字段名】字段格式错误</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="88" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>金额异常</x:v>
       </x:c>
@@ -962,22 +934,28 @@
       <x:c r="D6" s="9" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="E6" s="9" t="str">
+        <x:v>【字段名】金额异常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="88" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>首错输出规则</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>同一订单命中多个字段或多类校验问题时，仅输出按优先级命中的首个失败原因</x:v>
+        <x:v>同一订单命中多个字段或多类校验问题时，仅输出按优先级命中的首个订单级失败原因</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>基础必填缺失 → 字段格式错误 → 金额异常 → 主续关系异常 → 重复订单 → 系统异常</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
+        <x:v>基础必填缺失 → 字段格式错误 → 金额异常 → 主续关系异常 → 重复订单</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>仅展示按校验优先级命中的首个订单级失败原因</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="88" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
@@ -990,8 +968,12 @@
       <x:c r="D8" s="9" t="str">
         <x:v>未匹配到父订单，或父子订单证件号不一致</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="E8" s="9" t="str">
+        <x:v>未匹配到父订单：未匹配到父订单，请核对父订单编号后重新上传。
+证件号不一致：父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="88" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>重复订单</x:v>
       </x:c>
@@ -1004,39 +986,49 @@
       <x:c r="D9" s="9" t="str">
         <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="E9" s="9" t="str">
+        <x:v>跨批次重复：该订单已在批次【批次号】导入，本次不允许重复导入。
+同批次已流转：该订单已流转，无法再次导入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="88" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>失败文案规范</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>字段格式与金额异常按统一格式输出，便于运营定位Excel列</x:v>
+        <x:v>订单级字段格式与金额异常按统一格式输出，便于运营定位Excel列</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>字段名+字段格式错误；字段名+金额异常；系统异常</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
+        <x:v>字段名+字段格式错误；字段名+金额异常</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>字段格式错误：字段名+字段格式错误；金额异常：字段名+金额异常</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="88" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>系统异常</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>单笔订单解析、校验或落库发生技术异常；任务级异常不进入订单明细</x:v>
+        <x:v>任务创建后，异步解析、校验或落库发生技术异常；按任务级失败处理</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>是</x:v>
+        <x:v>任务级失败</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
+        <x:v>页面提示“系统异常”，批次状态为导入失败，不写入订单明细</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str">
         <x:v>系统异常</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd47e9415b70c4c61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f0424c521864f67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1046,7 +1038,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="76" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1077,7 +1069,7 @@
         <x:v>提交后动作</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>点击导入后提交异步任务；处理完成弹出“导入完成”或“导入失败”，点击确定后返回案件导入管理列表。</x:v>
+        <x:v>上传阶段校验通过后创建异步任务；系统异常按任务级失败处理，页面提示后返回案件导入管理列表。</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
         <x:v>二期再进入导入处理详情处理材料。</x:v>
@@ -1088,7 +1080,7 @@
         <x:v>明细下载</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>在案件导入管理列表点击下载明细；下载批次全量订单最新结果，同一失败订单仅展示首个失败原因。</x:v>
+        <x:v>订单明细仅保留可定位到具体订单的成功或业务校验失败；模板错误、系统异常不进入订单明细。</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
         <x:v>二期处理详情可补充更细解析。</x:v>
@@ -1099,7 +1091,7 @@
         <x:v>文件级前置校验</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>订单编号为空、同一Excel订单编号重复、订单超过500条、文件超过50MB、必填列缺失等均上传失败，不创建导入任务。</x:v>
+        <x:v>任一订单编号为空、同一Excel存在任意重复订单、模板错误、订单超过500条或文件超过50MB时，整份文件上传失败，不创建任务。</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
         <x:v>二期材料包另行增加解压和文件命名校验。</x:v>
@@ -1163,7 +1155,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc498a921607b4adc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c8883b1fb2a45c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rfaffe21899a04c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R6fbe7662ad1d4d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Re0860f9179ec4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Ra9b7eb871e0e4713"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R34e000b0c5984fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Rdbaa5530443044f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R783d5d15929945c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="41">
+  <x:fills count="42">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -335,6 +336,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -642,7 +648,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -722,6 +728,20 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -960,7 +980,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1" displayName="Table1" ref="A1:Q18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1" displayName="Table1" ref="A1:Q19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1003,6 +1023,22 @@
     <x:tableColumn id="1" name="口径项"/>
     <x:tableColumn id="2" name="统一口径"/>
     <x:tableColumn id="3" name="二期处理规则"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table4" displayName="Table4" ref="A1:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="订单编号"/>
+    <x:tableColumn id="2" name="客户姓名"/>
+    <x:tableColumn id="3" name="标准材料类别"/>
+    <x:tableColumn id="4" name="缺失材料名称"/>
+    <x:tableColumn id="5" name="材料要求"/>
+    <x:tableColumn id="6" name="案件状态"/>
+    <x:tableColumn id="7" name="处理结果"/>
+    <x:tableColumn id="8" name="导入时间"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1262,16 +1298,16 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="28" t="str">
+      <x:c r="N1" s="30" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="29" t="str">
+      <x:c r="O1" s="31" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="29" t="str">
+      <x:c r="P1" s="31" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="29" t="str">
+      <x:c r="Q1" s="31" t="str">
         <x:v>导入时间</x:v>
       </x:c>
       <x:c r="R1" t="str"/>
@@ -2166,10 +2202,64 @@
       </x:c>
       <x:c r="R18" t="str"/>
     </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>DR202606120003</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="str">
+        <x:v>创新租赁一期Excel导入批次04</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="str">
+        <x:v>创新</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="str">
+        <x:v>租赁</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="str">
+        <x:v>26012915050167612348</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="str">
+        <x:v>丁磊</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="str">
+        <x:v>420106199201010011</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str">
+        <x:v>导入成功</x:v>
+      </x:c>
+      <x:c r="I19" s="16" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="str">
+        <x:v>待补必填</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="str">
+        <x:v>租赁服务合同；订单详情-物流</x:v>
+      </x:c>
+      <x:c r="L19" s="16" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="N19" s="16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="O19" s="16" t="str">
+        <x:v>字段校验通过，缺少必填材料：租赁服务合同；缺少非必填材料：订单详情-物流。</x:v>
+      </x:c>
+      <x:c r="P19" s="16" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="Q19" s="16" t="str">
+        <x:v>2026-06-12 10:12:08</x:v>
+      </x:c>
+      <x:c r="R19" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb13fd7a958047ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1981a6f7155040ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2469,7 +2559,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47aaf63a16ed4234"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12126b5c966141d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2684,7 +2774,185 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ce4e500ca56462e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1bca1022f248f6"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="31" t="str">
+        <x:v>订单编号</x:v>
+      </x:c>
+      <x:c r="B1" s="31" t="str">
+        <x:v>客户姓名</x:v>
+      </x:c>
+      <x:c r="C1" s="31" t="str">
+        <x:v>标准材料类别</x:v>
+      </x:c>
+      <x:c r="D1" s="31" t="str">
+        <x:v>缺失材料名称</x:v>
+      </x:c>
+      <x:c r="E1" s="31" t="str">
+        <x:v>材料要求</x:v>
+      </x:c>
+      <x:c r="F1" s="31" t="str">
+        <x:v>案件状态</x:v>
+      </x:c>
+      <x:c r="G1" s="31" t="str">
+        <x:v>处理结果</x:v>
+      </x:c>
+      <x:c r="H1" s="31" t="str">
+        <x:v>导入时间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="16" t="str">
+        <x:v>26012915050167612342</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>孙悦</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>主合同</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>租赁服务合同</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str">
+        <x:v>2026-06-12 09:20:16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>26012915050167612343</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>林浩</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>订单信息</x:v>
+      </x:c>
+      <x:c r="D3" s="16" t="str">
+        <x:v>订单详情-物流</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="str">
+        <x:v>非必填</x:v>
+      </x:c>
+      <x:c r="F3" s="16" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="G3" s="16" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="H3" s="16" t="str">
+        <x:v>2026-06-12 09:20:16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>26012915050167612348</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>丁磊</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>主合同</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>租赁服务合同</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>2026-06-12 10:12:08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>26012915050167612348</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>丁磊</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>订单信息</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>订单详情-物流</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>非必填</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str">
+        <x:v>2026-06-12 10:12:08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>26012915050167612001</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>吴静</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>主合同</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>租赁服务合同</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="str">
+        <x:v>已生效</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>2026-06-12 10:15:26</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R603c49e1e6ab4612"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Ra9b7eb871e0e4713"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R34e000b0c5984fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Rdbaa5530443044f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R783d5d15929945c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R66183fca4dd54951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="Rb7a959415870413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R72538b885fae4935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Re4c07d67d45140e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="42">
+  <x:fills count="44">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -336,6 +336,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -648,7 +658,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -742,6 +752,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="42" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="42" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="43" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -980,7 +1002,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table1" displayName="Table1" ref="A1:Q19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table1" displayName="Table1" ref="A1:Q19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1029,7 +1051,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table4" displayName="Table4" ref="A1:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table4" displayName="Table4" ref="A1:H7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
@@ -1298,16 +1320,16 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="30" t="str">
+      <x:c r="N1" s="38" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="31" t="str">
+      <x:c r="O1" s="39" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="31" t="str">
+      <x:c r="P1" s="39" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="31" t="str">
+      <x:c r="Q1" s="39" t="str">
         <x:v>导入时间</x:v>
       </x:c>
       <x:c r="R1" t="str"/>
@@ -1933,12 +1955,8 @@
       <x:c r="L13" s="16" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="str">
-        <x:v>主合同</x:v>
-      </x:c>
-      <x:c r="N13" s="16" t="str">
-        <x:v>租赁服务合同</x:v>
-      </x:c>
+      <x:c r="M13" s="16" t="str"/>
+      <x:c r="N13" s="16" t="str"/>
       <x:c r="O13" s="16" t="str">
         <x:v>字段校验通过，缺少必填材料：租赁服务合同。</x:v>
       </x:c>
@@ -1987,12 +2005,8 @@
       <x:c r="L14" s="16" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="str">
-        <x:v>订单信息</x:v>
-      </x:c>
-      <x:c r="N14" s="16" t="str">
-        <x:v>订单详情-物流</x:v>
-      </x:c>
+      <x:c r="M14" s="16" t="str"/>
+      <x:c r="N14" s="16" t="str"/>
       <x:c r="O14" s="16" t="str">
         <x:v>字段校验通过，缺少非必填材料：订单详情-物流。</x:v>
       </x:c>
@@ -2234,19 +2248,15 @@
         <x:v>待补必填</x:v>
       </x:c>
       <x:c r="K19" s="16" t="str">
-        <x:v>租赁服务合同；订单详情-物流</x:v>
+        <x:v>租赁服务合同；租赁服务合同验签报告</x:v>
       </x:c>
       <x:c r="L19" s="16" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M19" s="16" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="N19" s="16" t="str">
-        <x:v>-</x:v>
-      </x:c>
+      <x:c r="M19" s="16" t="str"/>
+      <x:c r="N19" s="16" t="str"/>
       <x:c r="O19" s="16" t="str">
-        <x:v>字段校验通过，缺少必填材料：租赁服务合同；缺少非必填材料：订单详情-物流。</x:v>
+        <x:v>字段校验通过，缺少必填材料：租赁服务合同；租赁服务合同验签报告。</x:v>
       </x:c>
       <x:c r="P19" s="16" t="str">
         <x:v>否</x:v>
@@ -2259,7 +2269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1981a6f7155040ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0a6dd0110a4421b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2559,7 +2569,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12126b5c966141d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d274ed218634d86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2774,7 +2784,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1bca1022f248f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9e7383be134c78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2794,28 +2804,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="31" t="str">
+      <x:c r="A1" s="39" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="31" t="str">
+      <x:c r="B1" s="39" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="31" t="str">
+      <x:c r="C1" s="39" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="31" t="str">
+      <x:c r="D1" s="39" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="31" t="str">
+      <x:c r="E1" s="39" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="31" t="str">
+      <x:c r="F1" s="39" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="31" t="str">
+      <x:c r="G1" s="39" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="31" t="str">
+      <x:c r="H1" s="39" t="str">
         <x:v>导入时间</x:v>
       </x:c>
     </x:row>
@@ -2905,19 +2915,19 @@
         <x:v>丁磊</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>订单信息</x:v>
+        <x:v>主合同</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>订单详情-物流</x:v>
+        <x:v>租赁服务合同验签报告</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>非必填</x:v>
+        <x:v>必填</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str">
-        <x:v>缺少非必填材料</x:v>
+        <x:v>缺少必填材料</x:v>
       </x:c>
       <x:c r="H5" s="16" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
@@ -2925,34 +2935,60 @@
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="16" t="str">
+        <x:v>26012915050167612348</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>丁磊</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>订单信息</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>订单详情-物流</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>非必填</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="str">
+        <x:v>待材料激活</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="str">
+        <x:v>缺少非必填材料</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>2026-06-12 10:12:08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="16" t="str">
         <x:v>26012915050167612001</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B7" s="16" t="str">
         <x:v>吴静</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
+      <x:c r="C7" s="16" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="str">
+      <x:c r="D7" s="16" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="str">
+      <x:c r="E7" s="16" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F6" s="16" t="str">
+      <x:c r="F7" s="16" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="G6" s="16" t="str">
+      <x:c r="G7" s="16" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="str">
+      <x:c r="H7" s="16" t="str">
         <x:v>2026-06-12 10:15:26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R603c49e1e6ab4612"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd0b8087a49e48ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R66183fca4dd54951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="Rb7a959415870413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R72538b885fae4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Re4c07d67d45140e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R071efb6777c64faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R3dba064653914404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R744e6b689fc144ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Rcb2218cb1bc147a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="44">
+  <x:fills count="45">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -336,6 +336,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -658,7 +663,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,6 +769,20 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="43" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -1002,8 +1021,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table1" displayName="Table1" ref="A1:Q19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="18">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
     <x:tableColumn id="3" name="外部资产方"/>
@@ -1021,6 +1040,7 @@
     <x:tableColumn id="15" name="处理结果"/>
     <x:tableColumn id="16" name="是否阻断导入"/>
     <x:tableColumn id="17" name="导入时间"/>
+    <x:tableColumn id="18" name="业务主体1"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1051,8 +1071,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table4" displayName="Table4" ref="A1:H7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
     <x:tableColumn id="3" name="标准材料类别"/>
@@ -1061,6 +1081,7 @@
     <x:tableColumn id="6" name="案件状态"/>
     <x:tableColumn id="7" name="处理结果"/>
     <x:tableColumn id="8" name="导入时间"/>
+    <x:tableColumn id="9" name="业务主体1"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1278,6 +1299,7 @@
     <x:col min="15" max="15" width="48" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="36" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
@@ -1320,19 +1342,21 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="38" t="str">
+      <x:c r="N1" s="40" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="39" t="str">
+      <x:c r="O1" s="41" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="39" t="str">
+      <x:c r="P1" s="41" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="39" t="str">
+      <x:c r="Q1" s="41" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="R1" t="str"/>
+      <x:c r="R1" s="41" t="str">
+        <x:v>业务主体1</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="13" t="str">
@@ -1380,7 +1404,9 @@
       <x:c r="Q2" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R2" t="str"/>
+      <x:c r="R2" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="13" t="str">
@@ -1432,7 +1458,9 @@
       <x:c r="Q3" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R3" t="str"/>
+      <x:c r="R3" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -1486,7 +1514,9 @@
       <x:c r="Q4" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R4" t="str"/>
+      <x:c r="R4" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="13" t="str">
@@ -1540,7 +1570,9 @@
       <x:c r="Q5" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R5" t="str"/>
+      <x:c r="R5" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="13" t="str">
@@ -1594,7 +1626,9 @@
       <x:c r="Q6" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R6" t="str"/>
+      <x:c r="R6" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="13" t="str">
@@ -1648,7 +1682,9 @@
       <x:c r="Q7" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R7" t="str"/>
+      <x:c r="R7" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" s="13" t="str">
@@ -1702,7 +1738,9 @@
       <x:c r="Q8" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R8" t="str"/>
+      <x:c r="R8" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="13" t="str">
@@ -1754,7 +1792,9 @@
       <x:c r="Q9" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R9" t="str"/>
+      <x:c r="R9" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="13" t="str">
@@ -1808,7 +1848,9 @@
       <x:c r="Q10" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R10" t="str"/>
+      <x:c r="R10" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="13" t="str">
@@ -1862,7 +1904,9 @@
       <x:c r="Q11" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R11" t="str"/>
+      <x:c r="R11" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="13" t="str">
@@ -1916,7 +1960,9 @@
       <x:c r="Q12" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R12" t="str"/>
+      <x:c r="R12" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="16" t="str">
@@ -1966,7 +2012,9 @@
       <x:c r="Q13" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R13" t="str"/>
+      <x:c r="R13" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="16" t="str">
@@ -2016,7 +2064,9 @@
       <x:c r="Q14" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R14" t="str"/>
+      <x:c r="R14" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="16" t="str">
@@ -2064,7 +2114,9 @@
       <x:c r="Q15" s="16" t="str">
         <x:v>2026-06-12 10:05:18</x:v>
       </x:c>
-      <x:c r="R15" t="str"/>
+      <x:c r="R15" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="16" t="str">
@@ -2118,7 +2170,9 @@
       <x:c r="Q16" s="16" t="str">
         <x:v>2026-06-12 10:06:42</x:v>
       </x:c>
-      <x:c r="R16" t="str"/>
+      <x:c r="R16" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="16" t="str">
@@ -2134,13 +2188,13 @@
         <x:v>租赁</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
-        <x:v>26012915050167612346</x:v>
+        <x:v>26012915050167612347</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
-        <x:v>陈敏</x:v>
+        <x:v>郑楠</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str">
-        <x:v>420106199201010009</x:v>
+        <x:v>420106199201010010</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str">
         <x:v>导入成功</x:v>
@@ -2158,15 +2212,17 @@
       <x:c r="M17" s="16" t="str"/>
       <x:c r="N17" s="16" t="str"/>
       <x:c r="O17" s="16" t="str">
-        <x:v>强制覆盖成功：“是否强制覆盖”=是，已更新可覆盖字段。</x:v>
+        <x:v>主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新。</x:v>
       </x:c>
       <x:c r="P17" s="16" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="Q17" s="16" t="str">
-        <x:v>2026-06-12 10:08:16</x:v>
-      </x:c>
-      <x:c r="R17" t="str"/>
+        <x:v>2026-06-12 10:10:34</x:v>
+      </x:c>
+      <x:c r="R17" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="16" t="str">
@@ -2182,39 +2238,43 @@
         <x:v>租赁</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
-        <x:v>26012915050167612347</x:v>
+        <x:v>26012915050167612348</x:v>
       </x:c>
       <x:c r="F18" s="16" t="str">
-        <x:v>郑楠</x:v>
+        <x:v>丁磊</x:v>
       </x:c>
       <x:c r="G18" s="16" t="str">
-        <x:v>420106199201010010</x:v>
+        <x:v>420106199201010011</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str">
         <x:v>导入成功</x:v>
       </x:c>
       <x:c r="I18" s="16" t="str">
-        <x:v>已生效</x:v>
+        <x:v>待材料激活</x:v>
       </x:c>
       <x:c r="J18" s="16" t="str">
-        <x:v>材料齐全</x:v>
+        <x:v>待补必填</x:v>
       </x:c>
       <x:c r="K18" s="16" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L18" s="16" t="str"/>
+        <x:v>租赁服务合同；租赁服务合同验签报告</x:v>
+      </x:c>
+      <x:c r="L18" s="16" t="str">
+        <x:v>缺少必填材料</x:v>
+      </x:c>
       <x:c r="M18" s="16" t="str"/>
       <x:c r="N18" s="16" t="str"/>
       <x:c r="O18" s="16" t="str">
-        <x:v>主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新。</x:v>
+        <x:v>字段校验通过，缺少必填材料：租赁服务合同；租赁服务合同验签报告。</x:v>
       </x:c>
       <x:c r="P18" s="16" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="Q18" s="16" t="str">
-        <x:v>2026-06-12 10:10:34</x:v>
-      </x:c>
-      <x:c r="R18" t="str"/>
+        <x:v>2026-06-12 10:12:08</x:v>
+      </x:c>
+      <x:c r="R18" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" s="16" t="str">
@@ -2269,7 +2329,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0a6dd0110a4421b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e935a5fbd549e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2537,16 +2597,16 @@
         <x:v>覆盖成功口径</x:v>
       </x:c>
       <x:c r="B15" s="19" t="str">
-        <x:v>同批次订单未分配且未流转时自动覆盖；填写“是否强制覆盖=是”时强制覆盖。</x:v>
+        <x:v>同批次订单未分配且未流转时自动覆盖。</x:v>
       </x:c>
       <x:c r="C15" s="19" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
-        <x:v>同批次覆盖成功 / 强制覆盖成功</x:v>
+        <x:v>同批次覆盖成功</x:v>
       </x:c>
       <x:c r="E15" s="19" t="str">
-        <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；普通导入的处理结果为“成功”。同批次覆盖或强制覆盖时，处理结果分别为“同批次覆盖成功：使用后传Excel字段覆盖已有订单”或“强制覆盖成功：是否强制覆盖=是，已更新可覆盖字段”。</x:v>
+        <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；普通导入的处理结果为“成功”。同批次覆盖时，处理结果为“同批次覆盖成功：使用后传Excel字段覆盖已有订单”。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2569,7 +2629,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d274ed218634d86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bbca7458102469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2784,7 +2844,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9e7383be134c78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfac3bd0376404334"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2801,32 +2861,36 @@
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="39" t="str">
+      <x:c r="A1" s="41" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="39" t="str">
+      <x:c r="B1" s="41" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="39" t="str">
+      <x:c r="C1" s="41" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="39" t="str">
+      <x:c r="D1" s="41" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="39" t="str">
+      <x:c r="E1" s="41" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="39" t="str">
+      <x:c r="F1" s="41" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="39" t="str">
+      <x:c r="G1" s="41" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="39" t="str">
+      <x:c r="H1" s="41" t="str">
         <x:v>导入时间</x:v>
+      </x:c>
+      <x:c r="I1" s="41" t="str">
+        <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
@@ -2854,6 +2918,9 @@
       <x:c r="H2" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
+      <x:c r="I2" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="16" t="str">
@@ -2880,6 +2947,9 @@
       <x:c r="H3" s="16" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
+      <x:c r="I3" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="16" t="str">
@@ -2906,6 +2976,9 @@
       <x:c r="H4" s="16" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="16" t="str">
@@ -2932,6 +3005,9 @@
       <x:c r="H5" s="16" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
+      <x:c r="I5" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="16" t="str">
@@ -2958,6 +3034,9 @@
       <x:c r="H6" s="16" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>雅安欣天下办公设备租赁有限公司</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="16" t="str">
@@ -2984,11 +3063,14 @@
       <x:c r="H7" s="16" t="str">
         <x:v>2026-06-12 10:15:26</x:v>
       </x:c>
+      <x:c r="I7" s="16" t="str">
+        <x:v>雅安青年优品电子商务有限公司</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd0b8087a49e48ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43202f14d0f44413"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R071efb6777c64faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R3dba064653914404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R744e6b689fc144ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Rcb2218cb1bc147a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rd3651e10d11a462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R6ce78a79c3f14227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R708db24aab3d48de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R927aa894176244d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="45">
+  <x:fills count="49">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -336,6 +336,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -663,7 +683,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -783,6 +803,36 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="45" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="45" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="46" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="46" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="47" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="47" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="48" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="48" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -1021,7 +1071,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1071,7 +1121,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
@@ -1342,19 +1392,19 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="40" t="str">
+      <x:c r="N1" s="54" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="41" t="str">
+      <x:c r="O1" s="55" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="41" t="str">
+      <x:c r="P1" s="55" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="41" t="str">
+      <x:c r="Q1" s="55" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="R1" s="41" t="str">
+      <x:c r="R1" s="55" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
@@ -2081,13 +2131,13 @@
       <x:c r="D15" s="16" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="str">
+      <x:c r="E15" s="18" t="str">
         <x:v>26012915050167612344</x:v>
       </x:c>
-      <x:c r="F15" s="16" t="str">
+      <x:c r="F15" s="18" t="str">
         <x:v>许诺</x:v>
       </x:c>
-      <x:c r="G15" s="16" t="str">
+      <x:c r="G15" s="18" t="str">
         <x:v>420106199201010007</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str">
@@ -2131,13 +2181,13 @@
       <x:c r="D16" s="16" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="str">
+      <x:c r="E16" s="18" t="str">
         <x:v>26012915050167612345</x:v>
       </x:c>
-      <x:c r="F16" s="16" t="str">
+      <x:c r="F16" s="18" t="str">
         <x:v>周薇</x:v>
       </x:c>
-      <x:c r="G16" s="16" t="str">
+      <x:c r="G16" s="18" t="str">
         <x:v>420106199201010008</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str">
@@ -2187,13 +2237,13 @@
       <x:c r="D17" s="16" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="str">
+      <x:c r="E17" s="18" t="str">
         <x:v>26012915050167612347</x:v>
       </x:c>
-      <x:c r="F17" s="16" t="str">
+      <x:c r="F17" s="18" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G17" s="16" t="str">
+      <x:c r="G17" s="18" t="str">
         <x:v>420106199201010010</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str">
@@ -2237,13 +2287,13 @@
       <x:c r="D18" s="16" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="str">
+      <x:c r="E18" s="18" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="F18" s="16" t="str">
+      <x:c r="F18" s="18" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="G18" s="16" t="str">
+      <x:c r="G18" s="18" t="str">
         <x:v>420106199201010011</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str">
@@ -2329,7 +2379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e935a5fbd549e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cc1450e050f40bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2593,43 +2643,60 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="19" t="str">
+      <x:c r="A15" s="48" t="str">
         <x:v>覆盖成功口径</x:v>
       </x:c>
-      <x:c r="B15" s="19" t="str">
+      <x:c r="B15" s="48" t="str">
         <x:v>同批次订单未分配且未流转时自动覆盖。</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="str">
+      <x:c r="C15" s="48" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="str">
+      <x:c r="D15" s="48" t="str">
         <x:v>同批次覆盖成功</x:v>
       </x:c>
-      <x:c r="E15" s="19" t="str">
+      <x:c r="E15" s="48" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；普通导入的处理结果为“成功”。同批次覆盖时，处理结果为“同批次覆盖成功：使用后传Excel字段覆盖已有订单”。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="19" t="str">
+      <x:c r="A16" s="48" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="B16" s="19" t="str">
+      <x:c r="B16" s="48" t="str">
         <x:v>本次同时导入主订单和续租订单，系统中已存在对应主子订单案件且均未流转。</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="str">
+      <x:c r="C16" s="48" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D16" s="19" t="str">
+      <x:c r="D16" s="48" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="E16" s="19" t="str">
+      <x:c r="E16" s="48" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；处理结果为“主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新”。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="53" t="str">
+        <x:v>最终结果保留口径</x:v>
+      </x:c>
+      <x:c r="B17" s="53" t="str">
+        <x:v>订单已为导入成功且待材料激活，后续再次上传Excel但本次字段校验失败。</x:v>
+      </x:c>
+      <x:c r="C17" s="53" t="str">
+        <x:v>本次记录失败；不覆盖订单最终结果</x:v>
+      </x:c>
+      <x:c r="D17" s="53" t="str">
+        <x:v>下载明细仍为导入成功 / 待材料激活 / 待补必填</x:v>
+      </x:c>
+      <x:c r="E17" s="53" t="str">
+        <x:v>本次Excel失败写入批次处理记录；下载明细按订单当前最终结果展示，处理结果保留当前缺失材料说明。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bbca7458102469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e00158230e64d4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2703,54 +2770,54 @@
         <x:v>材料包上传</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>新建二期批次须同时上传Excel和材料包；材料包格式支持zip、rar、7z。</x:v>
+        <x:v>新建二期批次须同时上传Excel和材料包；材料包仅支持zip。</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>未上传材料包时整批不能提交导入；材料包解析异常不影响其它订单的字段处理。</x:v>
+        <x:v>未上传材料包或上传非zip格式时整批不能提交；材料包解析异常不影响其它订单的字段处理。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="13" t="str">
-        <x:v>异步处理</x:v>
+        <x:v>草稿与批次状态</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>点击导入后创建异步任务，页面展示“导入中”；任务结束后提示导入完成或导入失败。</x:v>
+        <x:v>本期不提供保存草稿；未提交页面取消后不创建批次。</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>确认提示后返回案件导入管理，可进入导入处理详情或下载明细查看处理结果。</x:v>
+        <x:v>批次导入状态仅为导入中、导入完成、导入失败。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="13" t="str">
-        <x:v>案件状态</x:v>
+        <x:v>异步处理</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>已生效：字段及必填材料均满足；待材料激活：字段通过但缺少必填材料；导入失败：订单字段或业务校验未通过。</x:v>
+        <x:v>点击导入后创建异步任务，页面展示“导入中”；任务结束后进入导入完成或导入失败。</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>待材料激活订单补齐必填材料并解析通过后自动变更为已生效。</x:v>
+        <x:v>确认提示后返回案件导入管理，可进入导入处理详情或下载明细查看处理结果。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="13" t="str">
-        <x:v>材料状态</x:v>
+        <x:v>案件状态</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>材料齐全、待补必填、待补非必填、未生成四种状态；待补材料展示当前缺失材料名称。</x:v>
+        <x:v>已生效：字段及必填材料均满足；待材料激活：字段通过但缺少必填材料；导入失败：订单字段或业务校验未通过。</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
-        <x:v>缺少非必填材料不影响案件生效；材料异常文件在“异常文件”中查看，不作为订单材料状态枚举。</x:v>
+        <x:v>待材料激活订单补齐必填材料并解析通过后自动变更为已生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>材料解析</x:v>
+        <x:v>材料状态</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
-        <x:v>系统按订单编号及材料规则自动识别材料大类、材料名称和必填性。</x:v>
+        <x:v>材料齐全、待补必填、待补非必填、未生成四种状态；待补材料展示当前缺失材料名称。</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
-        <x:v>不提供单文件上传和人工绑定；无法识别或未匹配规则的文件进入异常文件清单，支持随批量补传再次解析。</x:v>
+        <x:v>缺少非必填材料不影响案件生效；材料异常文件在“异常文件”中查看。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -2758,43 +2825,43 @@
         <x:v>批量补传</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
-        <x:v>同一批次可分多次上传，每次建议不超过500条订单。</x:v>
+        <x:v>同一批次可分多次上传，每次订单Excel最多500条。</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
-        <x:v>一个入口支持新增订单及材料、失败订单重新导入、仅补缺失材料、仅补充订单Excel；处理结果累计归集在原批次。</x:v>
+        <x:v>支持新增订单及材料、失败订单重新导入、仅补缺失材料、仅补订单Excel；处理过程归集在原批次。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>重复与覆盖</x:v>
+        <x:v>最终结果导出</x:v>
       </x:c>
       <x:c r="B12" s="16" t="str">
-        <x:v>跨批次同一资产方订单不允许重复导入；同批次再次导入时按订单当前案件状态判断是否可覆盖。</x:v>
+        <x:v>下载明细按订单当前最终结果导出，不按最后一次上传动作覆盖既有结果。</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str">
-        <x:v>案件已生效且已流转的订单不可覆盖；未流转且满足覆盖条件的订单可使用新上传Excel字段更新。</x:v>
+        <x:v>待材料激活订单后续Excel校验失败时，仍展示导入成功、待材料激活、待补必填；本次失败仅写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>主续订单</x:v>
+        <x:v>重复与覆盖</x:v>
       </x:c>
       <x:c r="B13" s="16" t="str">
-        <x:v>首次导入续租订单时，主订单须同批导入且为已结清状态；首次导入主订单后，不允许再导入对应续租订单。</x:v>
+        <x:v>跨批次同一资产方订单不允许重复导入；同批次再次导入时按订单当前案件状态判断是否可覆盖。</x:v>
       </x:c>
       <x:c r="C13" s="16" t="str">
-        <x:v>主子订单同批复导且案件均未流转时可更新；仅已有主订单或单独导入续租订单时，按主续关系异常阻断。</x:v>
+        <x:v>案件已流转的订单不可覆盖；未流转且满足条件的订单可使用新上传Excel字段更新。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>批次统计</x:v>
+        <x:v>主续订单</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>资产总数、导入成功、导入失败按订单编号去重，取该批次订单当前最新有效处理结果。</x:v>
+        <x:v>首次导入续租订单时，主订单须同批导入且为已结清状态；首次导入主订单后，不允许再导入对应续租订单。</x:v>
       </x:c>
       <x:c r="C14" s="16" t="str">
-        <x:v>材料处理状态单独统计；同一批次多次补传不会重复累加同一订单。</x:v>
+        <x:v>主子订单同批复导且案件均未流转时可更新；仅已有主订单或单独导入续租订单时按主续关系异常阻断。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
@@ -2802,10 +2869,10 @@
         <x:v>历史批次补材</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>一期历史案件仅导入Excel，案件已生效；材料状态初始展示为“未校验（一期导入）”。</x:v>
+        <x:v>一期历史案件仅导入Excel，案件已生效；材料状态初始为待初始化（一期）。</x:v>
       </x:c>
       <x:c r="C15" s="16" t="str">
-        <x:v>可通过“补充历史材料”上传材料包；解析后更新材料状态，不影响待委外及后续法诉流程。</x:v>
+        <x:v>可通过补充历史材料上传ZIP材料包；解析后更新材料状态，不影响待委外及后续法诉流程。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -2816,7 +2883,7 @@
         <x:v>批次管理“下载明细”与导入处理详情“导出当前筛选订单明细”使用同一模板。</x:v>
       </x:c>
       <x:c r="C16" s="16" t="str">
-        <x:v>工作簿包含导入结果明细、失败分类说明、口径说明；导入结果明细可按案件状态、材料状态、待补材料筛选。</x:v>
+        <x:v>工作簿包含导入结果明细、待补材料明细、失败分类说明、口径说明。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
@@ -2838,13 +2905,13 @@
         <x:v>债权出让主体为文本输入，最多50字；附件用于留存债权转让协议、转账回单、补充协议等。</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
-        <x:v>单批次最多10个附件，支持pdf、图片、xlsx、xls、zip、7z、rar；已上传附件支持下载、删除。</x:v>
+        <x:v>单批次最多10个附件，支持pdf、图片、xlsx、xls、zip；已上传附件支持下载、删除。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfac3bd0376404334"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac55c60d349a4826"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2865,36 +2932,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="41" t="str">
+      <x:c r="A1" s="55" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="41" t="str">
+      <x:c r="B1" s="55" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="41" t="str">
+      <x:c r="C1" s="55" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="41" t="str">
+      <x:c r="D1" s="55" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="41" t="str">
+      <x:c r="E1" s="55" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="41" t="str">
+      <x:c r="F1" s="55" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="41" t="str">
+      <x:c r="G1" s="55" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="41" t="str">
+      <x:c r="H1" s="55" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="I1" s="41" t="str">
+      <x:c r="I1" s="55" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="18" t="str">
         <x:v>26012915050167612342</x:v>
       </x:c>
       <x:c r="B2" s="16" t="str">
@@ -2923,7 +2990,7 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="18" t="str">
         <x:v>26012915050167612343</x:v>
       </x:c>
       <x:c r="B3" s="16" t="str">
@@ -2952,7 +3019,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="18" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
@@ -2981,7 +3048,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A5" s="18" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
@@ -3010,7 +3077,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="16" t="str">
+      <x:c r="A6" s="18" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
@@ -3039,7 +3106,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="16" t="str">
+      <x:c r="A7" s="18" t="str">
         <x:v>26012915050167612001</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
@@ -3070,7 +3137,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43202f14d0f44413"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad0c82aaed8140cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="Rd3651e10d11a462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R6ce78a79c3f14227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R708db24aab3d48de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R927aa894176244d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R7d81f758c2a34406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R65bd8165209a4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Rd27098f063a74b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R4fa5545ecd2d4ce6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="49">
+  <x:fills count="51">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -336,6 +336,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -683,7 +693,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -832,6 +842,18 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="48" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="49" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="49" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="50" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="50" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1071,7 +1093,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1121,7 +1143,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
@@ -1392,19 +1414,19 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="54" t="str">
+      <x:c r="N1" s="58" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="55" t="str">
+      <x:c r="O1" s="59" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="55" t="str">
+      <x:c r="P1" s="59" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="55" t="str">
+      <x:c r="Q1" s="59" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="R1" s="55" t="str">
+      <x:c r="R1" s="59" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
@@ -2191,7 +2213,7 @@
         <x:v>420106199201010008</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str">
-        <x:v>导入失败</x:v>
+        <x:v>导入成功</x:v>
       </x:c>
       <x:c r="I16" s="16" t="str">
         <x:v>已生效</x:v>
@@ -2202,15 +2224,9 @@
       <x:c r="K16" s="16" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="str">
-        <x:v>重复订单</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="str">
-        <x:v>订单编号</x:v>
-      </x:c>
-      <x:c r="N16" s="16" t="str">
-        <x:v>26012915050167612345</x:v>
-      </x:c>
+      <x:c r="L16" s="16" t="str"/>
+      <x:c r="M16" s="16" t="str"/>
+      <x:c r="N16" s="16" t="str"/>
       <x:c r="O16" s="16" t="str">
         <x:v>重复跳过：该订单已分配或已流转，不可覆盖。</x:v>
       </x:c>
@@ -2379,7 +2395,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cc1450e050f40bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2034277d4c394dc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2554,7 +2570,7 @@
       </x:c>
       <x:c r="E9" s="13" t="str">
         <x:v>跨批次重复：导入结果=导入失败，失败分类=重复订单，处理结果为“该订单已在批次【批次号】导入，本次不允许重复导入”。
-同批次重复跳过：导入结果=导入失败，失败分类=重复订单，处理结果为“重复跳过：该订单已分配或已流转，不可覆盖”。</x:v>
+同批次重复跳过：导入结果=导入成功，案件状态和材料状态保持当前最终状态；失败分类、失败字段和字段值为空，处理结果为“重复跳过：该订单已分配或已流转，不可覆盖”；本次失败另写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -2696,7 +2712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e00158230e64d4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd33b182ea34fd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2911,7 +2927,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac55c60d349a4826"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5591f23c7444879"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2932,31 +2948,31 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="55" t="str">
+      <x:c r="A1" s="59" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="55" t="str">
+      <x:c r="B1" s="59" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="55" t="str">
+      <x:c r="C1" s="59" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="55" t="str">
+      <x:c r="D1" s="59" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="55" t="str">
+      <x:c r="E1" s="59" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="55" t="str">
+      <x:c r="F1" s="59" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="55" t="str">
+      <x:c r="G1" s="59" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="55" t="str">
+      <x:c r="H1" s="59" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="I1" s="55" t="str">
+      <x:c r="I1" s="59" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
@@ -3137,7 +3153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad0c82aaed8140cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd80f80dbcbba41eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R7d81f758c2a34406"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R65bd8165209a4ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Rd27098f063a74b7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R4fa5545ecd2d4ce6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R47bf201c01ab44cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R83fe00a579794bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R0f3b62c7a34b491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Rf1ece1d490324794"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="51">
+  <x:fills count="53">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -411,6 +411,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -693,7 +703,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -855,6 +865,30 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="23" fillId="50" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="24" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="52" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="52" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -1093,7 +1127,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1114,7 +1148,7 @@
     <x:tableColumn id="17" name="导入时间"/>
     <x:tableColumn id="18" name="业务主体1"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -1127,7 +1161,7 @@
     <x:tableColumn id="4" name="示例"/>
     <x:tableColumn id="5" name="提示文案"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -1138,12 +1172,12 @@
     <x:tableColumn id="2" name="统一口径"/>
     <x:tableColumn id="3" name="二期处理规则"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
@@ -1155,7 +1189,7 @@
     <x:tableColumn id="8" name="导入时间"/>
     <x:tableColumn id="9" name="业务主体1"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -1414,931 +1448,931 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="58" t="str">
+      <x:c r="N1" s="64" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="59" t="str">
+      <x:c r="O1" s="65" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="59" t="str">
+      <x:c r="P1" s="65" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="59" t="str">
+      <x:c r="Q1" s="65" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="R1" s="59" t="str">
+      <x:c r="R1" s="65" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="13" t="str">
+      <x:c r="A2" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
+      <x:c r="B2" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C2" s="13" t="str">
+      <x:c r="C2" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D2" s="13" t="str">
+      <x:c r="D2" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E2" s="17" t="str">
+      <x:c r="E2" s="61" t="str">
         <x:v>26012915050167612327</x:v>
       </x:c>
-      <x:c r="F2" s="17" t="str">
+      <x:c r="F2" s="61" t="str">
         <x:v>张三</x:v>
       </x:c>
-      <x:c r="G2" s="17" t="str">
+      <x:c r="G2" s="61" t="str">
         <x:v>420106199201018888</x:v>
       </x:c>
-      <x:c r="H2" s="13" t="str">
+      <x:c r="H2" s="60" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I2" s="13" t="str">
+      <x:c r="I2" s="60" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J2" s="13" t="str">
+      <x:c r="J2" s="60" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K2" s="13" t="str">
+      <x:c r="K2" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L2" s="13" t="str"/>
-      <x:c r="M2" s="13" t="str"/>
-      <x:c r="N2" s="13" t="str"/>
-      <x:c r="O2" s="16" t="str">
+      <x:c r="L2" s="60" t="str"/>
+      <x:c r="M2" s="60" t="str"/>
+      <x:c r="N2" s="60" t="str"/>
+      <x:c r="O2" s="62" t="str">
         <x:v>成功</x:v>
       </x:c>
-      <x:c r="P2" s="16" t="str">
+      <x:c r="P2" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q2" s="16" t="str">
+      <x:c r="Q2" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R2" s="16" t="str">
+      <x:c r="R2" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E3" s="17" t="str">
+      <x:c r="E3" s="61" t="str">
         <x:v>26012915050167612328</x:v>
       </x:c>
-      <x:c r="F3" s="17" t="str">
+      <x:c r="F3" s="61" t="str">
         <x:v>李明</x:v>
       </x:c>
-      <x:c r="G3" s="17" t="str">
+      <x:c r="G3" s="61" t="str">
         <x:v>420106199201019999</x:v>
       </x:c>
-      <x:c r="H3" s="13" t="str">
+      <x:c r="H3" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I3" s="13" t="str">
+      <x:c r="I3" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="str">
+      <x:c r="J3" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K3" s="13" t="str">
+      <x:c r="K3" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L3" s="13" t="str">
+      <x:c r="L3" s="60" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="M3" s="13" t="str">
+      <x:c r="M3" s="60" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="N3" s="13" t="str"/>
-      <x:c r="O3" s="16" t="str">
+      <x:c r="N3" s="60" t="str"/>
+      <x:c r="O3" s="62" t="str">
         <x:v>债权金额为必填字段，当前为空</x:v>
       </x:c>
-      <x:c r="P3" s="16" t="str">
+      <x:c r="P3" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q3" s="16" t="str">
+      <x:c r="Q3" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R3" s="16" t="str">
+      <x:c r="R3" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="A4" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
+      <x:c r="C4" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D4" s="13" t="str">
+      <x:c r="D4" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E4" s="17" t="str">
+      <x:c r="E4" s="61" t="str">
         <x:v>26012915050167612329</x:v>
       </x:c>
-      <x:c r="F4" s="17" t="str">
+      <x:c r="F4" s="61" t="str">
         <x:v>王磊</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="str">
+      <x:c r="G4" s="61" t="str">
         <x:v>42010619920101</x:v>
       </x:c>
-      <x:c r="H4" s="13" t="str">
+      <x:c r="H4" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I4" s="13" t="str">
+      <x:c r="I4" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J4" s="13" t="str">
+      <x:c r="J4" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K4" s="13" t="str">
+      <x:c r="K4" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L4" s="13" t="str">
+      <x:c r="L4" s="60" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="M4" s="13" t="str">
+      <x:c r="M4" s="60" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="N4" s="13" t="str">
+      <x:c r="N4" s="60" t="str">
         <x:v>42010619920101</x:v>
       </x:c>
-      <x:c r="O4" s="16" t="str">
+      <x:c r="O4" s="62" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-      <x:c r="P4" s="16" t="str">
+      <x:c r="P4" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q4" s="16" t="str">
+      <x:c r="Q4" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R4" s="16" t="str">
+      <x:c r="R4" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="13" t="str">
+      <x:c r="A5" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B5" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
+      <x:c r="C5" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D5" s="13" t="str">
+      <x:c r="D5" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="str">
+      <x:c r="E5" s="61" t="str">
         <x:v>26012915050167612330</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="str">
+      <x:c r="F5" s="61" t="str">
         <x:v>黄丽</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="str">
+      <x:c r="G5" s="61" t="str">
         <x:v>420106199201017777</x:v>
       </x:c>
-      <x:c r="H5" s="13" t="str">
+      <x:c r="H5" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I5" s="13" t="str">
+      <x:c r="I5" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="str">
+      <x:c r="J5" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K5" s="13" t="str">
+      <x:c r="K5" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L5" s="13" t="str">
+      <x:c r="L5" s="60" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="M5" s="13" t="str">
+      <x:c r="M5" s="60" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="N5" s="13" t="str">
+      <x:c r="N5" s="60" t="str">
         <x:v>-5999.00</x:v>
       </x:c>
-      <x:c r="O5" s="16" t="str">
+      <x:c r="O5" s="62" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-      <x:c r="P5" s="16" t="str">
+      <x:c r="P5" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q5" s="16" t="str">
+      <x:c r="Q5" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R5" s="16" t="str">
+      <x:c r="R5" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="13" t="str">
+      <x:c r="A6" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B6" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
+      <x:c r="C6" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D6" s="13" t="str">
+      <x:c r="D6" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E6" s="17" t="str">
+      <x:c r="E6" s="61" t="str">
         <x:v>26012915050167612331</x:v>
       </x:c>
-      <x:c r="F6" s="17" t="str">
+      <x:c r="F6" s="61" t="str">
         <x:v>周强</x:v>
       </x:c>
-      <x:c r="G6" s="17" t="str">
+      <x:c r="G6" s="61" t="str">
         <x:v>420106199201016666</x:v>
       </x:c>
-      <x:c r="H6" s="13" t="str">
+      <x:c r="H6" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I6" s="13" t="str">
+      <x:c r="I6" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J6" s="13" t="str">
+      <x:c r="J6" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="str">
+      <x:c r="K6" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L6" s="13" t="str">
+      <x:c r="L6" s="60" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="M6" s="13" t="str">
+      <x:c r="M6" s="60" t="str">
         <x:v>性别</x:v>
       </x:c>
-      <x:c r="N6" s="13" t="str">
+      <x:c r="N6" s="60" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="O6" s="16" t="str">
+      <x:c r="O6" s="62" t="str">
         <x:v>性别字段格式错误</x:v>
       </x:c>
-      <x:c r="P6" s="16" t="str">
+      <x:c r="P6" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q6" s="16" t="str">
+      <x:c r="Q6" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R6" s="16" t="str">
+      <x:c r="R6" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="13" t="str">
+      <x:c r="A7" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
+      <x:c r="B7" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="str">
+      <x:c r="C7" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="str">
+      <x:c r="D7" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="str">
+      <x:c r="E7" s="61" t="str">
         <x:v>26012915050167612332</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="str">
+      <x:c r="F7" s="61" t="str">
         <x:v>赵倩</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="str">
+      <x:c r="G7" s="61" t="str">
         <x:v>420106199201015555</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="str">
+      <x:c r="H7" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="str">
+      <x:c r="I7" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="str">
+      <x:c r="J7" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="str">
+      <x:c r="K7" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="str">
+      <x:c r="L7" s="60" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M7" s="13" t="str">
+      <x:c r="M7" s="60" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="N7" s="13" t="str">
+      <x:c r="N7" s="60" t="str">
         <x:v>26012915050167610001</x:v>
       </x:c>
-      <x:c r="O7" s="16" t="str">
+      <x:c r="O7" s="62" t="str">
         <x:v>父订单编号不存在，且本批次未导入对应主订单</x:v>
       </x:c>
-      <x:c r="P7" s="16" t="str">
+      <x:c r="P7" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q7" s="16" t="str">
+      <x:c r="Q7" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R7" s="16" t="str">
+      <x:c r="R7" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="13" t="str">
+      <x:c r="A8" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="str">
+      <x:c r="B8" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="str">
+      <x:c r="C8" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="str">
+      <x:c r="D8" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E8" s="17" t="str">
+      <x:c r="E8" s="61" t="str">
         <x:v>26012915050167612336</x:v>
       </x:c>
-      <x:c r="F8" s="17" t="str">
+      <x:c r="F8" s="61" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="G8" s="17" t="str">
+      <x:c r="G8" s="61" t="str">
         <x:v>420106199201010001</x:v>
       </x:c>
-      <x:c r="H8" s="13" t="str">
+      <x:c r="H8" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I8" s="13" t="str">
+      <x:c r="I8" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="str">
+      <x:c r="J8" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="str">
+      <x:c r="K8" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L8" s="13" t="str">
+      <x:c r="L8" s="60" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="str">
+      <x:c r="M8" s="60" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="N8" s="13" t="str">
+      <x:c r="N8" s="60" t="str">
         <x:v>420106199201010001</x:v>
       </x:c>
-      <x:c r="O8" s="16" t="str">
+      <x:c r="O8" s="62" t="str">
         <x:v>父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。</x:v>
       </x:c>
-      <x:c r="P8" s="16" t="str">
+      <x:c r="P8" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q8" s="16" t="str">
+      <x:c r="Q8" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R8" s="16" t="str">
+      <x:c r="R8" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="13" t="str">
+      <x:c r="A9" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B9" s="13" t="str">
+      <x:c r="B9" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="str">
+      <x:c r="C9" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="str">
+      <x:c r="D9" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E9" s="17" t="str">
+      <x:c r="E9" s="61" t="str">
         <x:v>26012915050167612337</x:v>
       </x:c>
-      <x:c r="F9" s="17" t="str">
+      <x:c r="F9" s="61" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="str">
+      <x:c r="G9" s="61" t="str">
         <x:v>420106199201010002</x:v>
       </x:c>
-      <x:c r="H9" s="13" t="str">
+      <x:c r="H9" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I9" s="13" t="str">
+      <x:c r="I9" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J9" s="13" t="str">
+      <x:c r="J9" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="str">
+      <x:c r="K9" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L9" s="13" t="str">
+      <x:c r="L9" s="60" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="str">
+      <x:c r="M9" s="60" t="str">
         <x:v>违约日</x:v>
       </x:c>
-      <x:c r="N9" s="13" t="str"/>
-      <x:c r="O9" s="16" t="str">
+      <x:c r="N9" s="60" t="str"/>
+      <x:c r="O9" s="62" t="str">
         <x:v>续租订单违约日不能为空，请补充后重新上传。</x:v>
       </x:c>
-      <x:c r="P9" s="16" t="str">
+      <x:c r="P9" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q9" s="16" t="str">
+      <x:c r="Q9" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R9" s="16" t="str">
+      <x:c r="R9" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="13" t="str">
+      <x:c r="A10" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="str">
+      <x:c r="B10" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="str">
+      <x:c r="C10" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D10" s="13" t="str">
+      <x:c r="D10" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="str">
+      <x:c r="E10" s="61" t="str">
         <x:v>26012915050167612333</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="str">
+      <x:c r="F10" s="61" t="str">
         <x:v>陈晨</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="str">
+      <x:c r="G10" s="61" t="str">
         <x:v>420106199201014444</x:v>
       </x:c>
-      <x:c r="H10" s="13" t="str">
+      <x:c r="H10" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I10" s="13" t="str">
+      <x:c r="I10" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J10" s="13" t="str">
+      <x:c r="J10" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K10" s="13" t="str">
+      <x:c r="K10" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L10" s="13" t="str">
+      <x:c r="L10" s="60" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="M10" s="13" t="str">
+      <x:c r="M10" s="60" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="N10" s="13" t="str">
+      <x:c r="N10" s="60" t="str">
         <x:v>26012915050167612333</x:v>
       </x:c>
-      <x:c r="O10" s="16" t="str">
+      <x:c r="O10" s="62" t="str">
         <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
       </x:c>
-      <x:c r="P10" s="16" t="str">
+      <x:c r="P10" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q10" s="16" t="str">
+      <x:c r="Q10" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R10" s="16" t="str">
+      <x:c r="R10" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="13" t="str">
+      <x:c r="A11" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B11" s="13" t="str">
+      <x:c r="B11" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C11" s="13" t="str">
+      <x:c r="C11" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D11" s="13" t="str">
+      <x:c r="D11" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="str">
+      <x:c r="E11" s="61" t="str">
         <x:v>26012915050167612340</x:v>
       </x:c>
-      <x:c r="F11" s="17" t="str">
+      <x:c r="F11" s="61" t="str">
         <x:v>刘洋</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="str">
+      <x:c r="G11" s="61" t="str">
         <x:v>420106199201010003</x:v>
       </x:c>
-      <x:c r="H11" s="13" t="str">
+      <x:c r="H11" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I11" s="13" t="str">
+      <x:c r="I11" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J11" s="13" t="str">
+      <x:c r="J11" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K11" s="13" t="str">
+      <x:c r="K11" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L11" s="13" t="str">
+      <x:c r="L11" s="60" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M11" s="13" t="str">
+      <x:c r="M11" s="60" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="N11" s="13" t="str">
+      <x:c r="N11" s="60" t="str">
         <x:v>26012915050167612327</x:v>
       </x:c>
-      <x:c r="O11" s="16" t="str">
+      <x:c r="O11" s="62" t="str">
         <x:v>续租订单关联的主订单【26012915050167612327】已在法诉系统形成案件，不符合续租订单导入条件。</x:v>
       </x:c>
-      <x:c r="P11" s="16" t="str">
+      <x:c r="P11" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q11" s="16" t="str">
+      <x:c r="Q11" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R11" s="16" t="str">
+      <x:c r="R11" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="13" t="str">
+      <x:c r="A12" s="60" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B12" s="13" t="str">
+      <x:c r="B12" s="60" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C12" s="13" t="str">
+      <x:c r="C12" s="60" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D12" s="13" t="str">
+      <x:c r="D12" s="60" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="str">
+      <x:c r="E12" s="61" t="str">
         <x:v>26012915050167612341</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="str">
+      <x:c r="F12" s="61" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="str">
+      <x:c r="G12" s="61" t="str">
         <x:v>420106199201010004</x:v>
       </x:c>
-      <x:c r="H12" s="13" t="str">
+      <x:c r="H12" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I12" s="13" t="str">
+      <x:c r="I12" s="60" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J12" s="13" t="str">
+      <x:c r="J12" s="60" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K12" s="13" t="str">
+      <x:c r="K12" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L12" s="13" t="str">
+      <x:c r="L12" s="60" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="M12" s="13" t="str">
+      <x:c r="M12" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="N12" s="13" t="str">
+      <x:c r="N12" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="O12" s="16" t="str">
+      <x:c r="O12" s="62" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="P12" s="16" t="str">
+      <x:c r="P12" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q12" s="16" t="str">
+      <x:c r="Q12" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R12" s="16" t="str">
+      <x:c r="R12" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
-      <x:c r="A13" s="16" t="str">
+      <x:c r="A13" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B13" s="16" t="str">
+      <x:c r="B13" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="str">
+      <x:c r="C13" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="str">
+      <x:c r="D13" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E13" s="18" t="str">
+      <x:c r="E13" s="63" t="str">
         <x:v>26012915050167612342</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="str">
+      <x:c r="F13" s="63" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="G13" s="18" t="str">
+      <x:c r="G13" s="63" t="str">
         <x:v>420106199201010005</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str">
+      <x:c r="H13" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I13" s="16" t="str">
+      <x:c r="I13" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="str">
+      <x:c r="J13" s="62" t="str">
         <x:v>待补必填</x:v>
       </x:c>
-      <x:c r="K13" s="16" t="str">
+      <x:c r="K13" s="62" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="L13" s="16" t="str">
+      <x:c r="L13" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="str"/>
-      <x:c r="N13" s="16" t="str"/>
-      <x:c r="O13" s="16" t="str">
+      <x:c r="M13" s="62" t="str"/>
+      <x:c r="N13" s="62" t="str"/>
+      <x:c r="O13" s="62" t="str">
         <x:v>字段校验通过，缺少必填材料：租赁服务合同。</x:v>
       </x:c>
-      <x:c r="P13" s="16" t="str">
+      <x:c r="P13" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q13" s="16" t="str">
+      <x:c r="Q13" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R13" s="16" t="str">
+      <x:c r="R13" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="16" t="str">
+      <x:c r="A14" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B14" s="16" t="str">
+      <x:c r="B14" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="str">
+      <x:c r="C14" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="str">
+      <x:c r="D14" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E14" s="18" t="str">
+      <x:c r="E14" s="63" t="str">
         <x:v>26012915050167612343</x:v>
       </x:c>
-      <x:c r="F14" s="18" t="str">
+      <x:c r="F14" s="63" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="G14" s="18" t="str">
+      <x:c r="G14" s="63" t="str">
         <x:v>420106199201010006</x:v>
       </x:c>
-      <x:c r="H14" s="16" t="str">
+      <x:c r="H14" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I14" s="16" t="str">
+      <x:c r="I14" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="str">
+      <x:c r="J14" s="62" t="str">
         <x:v>待补非必填</x:v>
       </x:c>
-      <x:c r="K14" s="16" t="str">
+      <x:c r="K14" s="62" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="L14" s="16" t="str">
+      <x:c r="L14" s="62" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="str"/>
-      <x:c r="N14" s="16" t="str"/>
-      <x:c r="O14" s="16" t="str">
+      <x:c r="M14" s="62" t="str"/>
+      <x:c r="N14" s="62" t="str"/>
+      <x:c r="O14" s="62" t="str">
         <x:v>字段校验通过，缺少非必填材料：订单详情-物流。</x:v>
       </x:c>
-      <x:c r="P14" s="16" t="str">
+      <x:c r="P14" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q14" s="16" t="str">
+      <x:c r="Q14" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R14" s="16" t="str">
+      <x:c r="R14" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="16" t="str">
+      <x:c r="A15" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B15" s="16" t="str">
+      <x:c r="B15" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="str">
+      <x:c r="C15" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="str">
+      <x:c r="D15" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E15" s="18" t="str">
+      <x:c r="E15" s="63" t="str">
         <x:v>26012915050167612344</x:v>
       </x:c>
-      <x:c r="F15" s="18" t="str">
+      <x:c r="F15" s="63" t="str">
         <x:v>许诺</x:v>
       </x:c>
-      <x:c r="G15" s="18" t="str">
+      <x:c r="G15" s="63" t="str">
         <x:v>420106199201010007</x:v>
       </x:c>
-      <x:c r="H15" s="16" t="str">
+      <x:c r="H15" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I15" s="16" t="str">
+      <x:c r="I15" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="str">
+      <x:c r="J15" s="62" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="str">
+      <x:c r="K15" s="62" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L15" s="16" t="str"/>
-      <x:c r="M15" s="16" t="str"/>
-      <x:c r="N15" s="16" t="str"/>
-      <x:c r="O15" s="16" t="str">
+      <x:c r="L15" s="62" t="str"/>
+      <x:c r="M15" s="62" t="str"/>
+      <x:c r="N15" s="62" t="str"/>
+      <x:c r="O15" s="62" t="str">
         <x:v>同批次覆盖成功：使用后传Excel字段覆盖已有订单。</x:v>
       </x:c>
-      <x:c r="P15" s="16" t="str">
+      <x:c r="P15" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q15" s="16" t="str">
+      <x:c r="Q15" s="62" t="str">
         <x:v>2026-06-12 10:05:18</x:v>
       </x:c>
-      <x:c r="R15" s="16" t="str">
+      <x:c r="R15" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
-      <x:c r="A16" s="16" t="str">
+      <x:c r="A16" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B16" s="16" t="str">
+      <x:c r="B16" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="str">
+      <x:c r="C16" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="str">
+      <x:c r="D16" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E16" s="18" t="str">
+      <x:c r="E16" s="63" t="str">
         <x:v>26012915050167612345</x:v>
       </x:c>
-      <x:c r="F16" s="18" t="str">
+      <x:c r="F16" s="63" t="str">
         <x:v>周薇</x:v>
       </x:c>
-      <x:c r="G16" s="18" t="str">
+      <x:c r="G16" s="63" t="str">
         <x:v>420106199201010008</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="str">
+      <x:c r="H16" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="str">
+      <x:c r="I16" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="str">
+      <x:c r="J16" s="62" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K16" s="16" t="str">
+      <x:c r="K16" s="62" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="str"/>
-      <x:c r="M16" s="16" t="str"/>
-      <x:c r="N16" s="16" t="str"/>
-      <x:c r="O16" s="16" t="str">
+      <x:c r="L16" s="62" t="str"/>
+      <x:c r="M16" s="62" t="str"/>
+      <x:c r="N16" s="62" t="str"/>
+      <x:c r="O16" s="62" t="str">
         <x:v>重复跳过：该订单已分配或已流转，不可覆盖。</x:v>
       </x:c>
-      <x:c r="P16" s="16" t="str">
+      <x:c r="P16" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q16" s="16" t="str">
+      <x:c r="Q16" s="62" t="str">
         <x:v>2026-06-12 10:06:42</x:v>
       </x:c>
-      <x:c r="R16" s="16" t="str">
+      <x:c r="R16" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
-      <x:c r="A17" s="16" t="str">
+      <x:c r="A17" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B17" s="16" t="str">
+      <x:c r="B17" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C17" s="16" t="str">
+      <x:c r="C17" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="str">
+      <x:c r="D17" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E17" s="18" t="str">
+      <x:c r="E17" s="63" t="str">
         <x:v>26012915050167612347</x:v>
       </x:c>
-      <x:c r="F17" s="18" t="str">
+      <x:c r="F17" s="63" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G17" s="18" t="str">
+      <x:c r="G17" s="63" t="str">
         <x:v>420106199201010010</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="str">
+      <x:c r="H17" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I17" s="16" t="str">
+      <x:c r="I17" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="str">
+      <x:c r="J17" s="62" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K17" s="16" t="str">
+      <x:c r="K17" s="62" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L17" s="16" t="str"/>
-      <x:c r="M17" s="16" t="str"/>
-      <x:c r="N17" s="16" t="str"/>
-      <x:c r="O17" s="16" t="str">
+      <x:c r="L17" s="62" t="str"/>
+      <x:c r="M17" s="62" t="str"/>
+      <x:c r="N17" s="62" t="str"/>
+      <x:c r="O17" s="62" t="str">
         <x:v>主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新。</x:v>
       </x:c>
-      <x:c r="P17" s="16" t="str">
+      <x:c r="P17" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q17" s="16" t="str">
+      <x:c r="Q17" s="62" t="str">
         <x:v>2026-06-12 10:10:34</x:v>
       </x:c>
-      <x:c r="R17" s="16" t="str">
+      <x:c r="R17" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
-      <x:c r="A18" s="16" t="str">
+      <x:c r="A18" s="62" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B18" s="16" t="str">
+      <x:c r="B18" s="62" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C18" s="16" t="str">
+      <x:c r="C18" s="62" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="str">
+      <x:c r="D18" s="62" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E18" s="18" t="str">
+      <x:c r="E18" s="63" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="str">
+      <x:c r="F18" s="63" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="G18" s="18" t="str">
+      <x:c r="G18" s="63" t="str">
         <x:v>420106199201010011</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="str">
+      <x:c r="H18" s="62" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I18" s="16" t="str">
+      <x:c r="I18" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="str">
+      <x:c r="J18" s="62" t="str">
         <x:v>待补必填</x:v>
       </x:c>
-      <x:c r="K18" s="16" t="str">
+      <x:c r="K18" s="62" t="str">
         <x:v>租赁服务合同；租赁服务合同验签报告</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="str">
+      <x:c r="L18" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="str"/>
-      <x:c r="N18" s="16" t="str"/>
-      <x:c r="O18" s="16" t="str">
+      <x:c r="M18" s="62" t="str"/>
+      <x:c r="N18" s="62" t="str"/>
+      <x:c r="O18" s="62" t="str">
         <x:v>字段校验通过，缺少必填材料：租赁服务合同；租赁服务合同验签报告。</x:v>
       </x:c>
-      <x:c r="P18" s="16" t="str">
+      <x:c r="P18" s="62" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q18" s="16" t="str">
+      <x:c r="Q18" s="62" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="R18" s="16" t="str">
+      <x:c r="R18" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
@@ -2395,7 +2429,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2034277d4c394dc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39b181e0a0234731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2429,19 +2463,19 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="13" t="str">
+      <x:c r="A2" s="60" t="str">
         <x:v>文件级前置校验</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
+      <x:c r="B2" s="60" t="str">
         <x:v>订单编号为空、同一Excel订单编号重复、必填列缺失、重复列头、文件超过50MB、订单超过500条</x:v>
       </x:c>
-      <x:c r="C2" s="13" t="str">
+      <x:c r="C2" s="60" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D2" s="13" t="str">
+      <x:c r="D2" s="60" t="str">
         <x:v>模板中有重复订单，请修正后重新上传。</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="str">
+      <x:c r="E2" s="60" t="str">
         <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
 重复订单：模板中有重复订单，请修正后重新上传。
 文件超过50MB：上传文件超过50MB，请压缩或拆分后重新上传。
@@ -2449,106 +2483,106 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="60" t="str">
         <x:v>模板格式错误</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="60" t="str">
         <x:v>文件无法解析、列头名称与模板不一致、缺少必填列等模板问题</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="60" t="str">
         <x:v>上传阶段拦截</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="60" t="str">
         <x:v>整份文件上传失败，不创建任务</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="60" t="str">
         <x:v>文件无法解析：文件无法解析，请确认文件未损坏且格式为xlsx/xls后重新上传。
 列头不一致：模板列头【实际列名】与标准模板不一致，请下载最新模板修正后重新上传。
 缺少必填列：模板缺少必填列【列名】，请修正后重新上传。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="A4" s="60" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="60" t="str">
         <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
+      <x:c r="C4" s="60" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D4" s="13" t="str">
+      <x:c r="D4" s="60" t="str">
         <x:v>续租订单违约日为空</x:v>
       </x:c>
-      <x:c r="E4" s="13" t="str">
+      <x:c r="E4" s="60" t="str">
         <x:v>【字段名】不能为空</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="13" t="str">
+      <x:c r="A5" s="60" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B5" s="60" t="str">
         <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
+      <x:c r="C5" s="60" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D5" s="13" t="str">
+      <x:c r="D5" s="60" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-      <x:c r="E5" s="13" t="str">
+      <x:c r="E5" s="60" t="str">
         <x:v>【字段名】字段格式错误</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="13" t="str">
+      <x:c r="A6" s="60" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B6" s="60" t="str">
         <x:v>金额非数字、负数，或金额关系不合法</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
+      <x:c r="C6" s="60" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D6" s="13" t="str">
+      <x:c r="D6" s="60" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-      <x:c r="E6" s="13" t="str">
+      <x:c r="E6" s="60" t="str">
         <x:v>【字段名】金额异常</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="13" t="str">
+      <x:c r="A7" s="60" t="str">
         <x:v>首错输出规则</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
+      <x:c r="B7" s="60" t="str">
         <x:v>同一订单命中多个字段或多类校验问题时，仅输出按优先级命中的首个订单级失败原因</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="str">
+      <x:c r="C7" s="60" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="str">
+      <x:c r="D7" s="60" t="str">
         <x:v>基础必填缺失 → 字段格式错误 → 金额异常 → 主续关系异常 → 重复订单</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="str">
+      <x:c r="E7" s="60" t="str">
         <x:v>仅展示按校验优先级命中的首个订单级失败原因</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="13" t="str">
+      <x:c r="A8" s="60" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="str">
+      <x:c r="B8" s="60" t="str">
         <x:v>首次导入续租订单时主订单未同批导入、主订单不是已结清状态、父子证件号不一致；或主订单已作为初始订单导入后再次导入续租订单</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="str">
+      <x:c r="C8" s="60" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="str">
+      <x:c r="D8" s="60" t="str">
         <x:v>主订单已作为初始订单导入后，再导入对应续租订单</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="str">
+      <x:c r="E8" s="60" t="str">
         <x:v>未匹配到父订单：未匹配到父订单，请将已结清主订单与续租订单一并导入后重新上传。
 主订单非已结清：父订单不是已结清状态，不符合续租订单导入条件。
 证件号不一致：父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。
@@ -2556,163 +2590,163 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="13" t="str">
+      <x:c r="A9" s="60" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="B9" s="13" t="str">
+      <x:c r="B9" s="60" t="str">
         <x:v>跨批次同一外部资产方+订单编号已存在；或同批次订单已分配/已流转，不可覆盖。</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="str">
+      <x:c r="C9" s="60" t="str">
         <x:v>跨批次：是；同批次跳过：否</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="str">
+      <x:c r="D9" s="60" t="str">
         <x:v>重复跳过</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="str">
+      <x:c r="E9" s="60" t="str">
         <x:v>跨批次重复：导入结果=导入失败，失败分类=重复订单，处理结果为“该订单已在批次【批次号】导入，本次不允许重复导入”。
 同批次重复跳过：导入结果=导入成功，案件状态和材料状态保持当前最终状态；失败分类、失败字段和字段值为空，处理结果为“重复跳过：该订单已分配或已流转，不可覆盖”；本次失败另写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="13" t="str">
+      <x:c r="A10" s="60" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="str">
+      <x:c r="B10" s="60" t="str">
         <x:v>订单字段校验通过，但材料包未匹配到导入规则要求的必填材料</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="str">
+      <x:c r="C10" s="60" t="str">
         <x:v>不阻断导入；案件待材料激活</x:v>
       </x:c>
-      <x:c r="D10" s="13" t="str">
+      <x:c r="D10" s="60" t="str">
         <x:v>缺少租赁服务合同</x:v>
       </x:c>
-      <x:c r="E10" s="13" t="str">
+      <x:c r="E10" s="60" t="str">
         <x:v>缺少必填材料：{材料名称}；请通过批量补传仅上传材料包。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="13" t="str">
+      <x:c r="A11" s="60" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="B11" s="13" t="str">
+      <x:c r="B11" s="60" t="str">
         <x:v>订单字段校验通过，但材料包未匹配到导入规则要求的非必填材料</x:v>
       </x:c>
-      <x:c r="C11" s="13" t="str">
+      <x:c r="C11" s="60" t="str">
         <x:v>不阻断导入；案件保持已生效</x:v>
       </x:c>
-      <x:c r="D11" s="13" t="str">
+      <x:c r="D11" s="60" t="str">
         <x:v>缺少订单详情-物流</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="str">
+      <x:c r="E11" s="60" t="str">
         <x:v>缺少非必填材料：{材料名称}；可按需通过批量补传仅上传材料包。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="16" t="str">
+      <x:c r="A12" s="62" t="str">
         <x:v>材料解析异常</x:v>
       </x:c>
-      <x:c r="B12" s="16" t="str">
+      <x:c r="B12" s="62" t="str">
         <x:v>材料包无法解压、文件无法识别订单归属或未匹配到材料规则</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="str">
+      <x:c r="C12" s="62" t="str">
         <x:v>不阻断其它订单导入</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="str">
+      <x:c r="D12" s="62" t="str">
         <x:v>订单编号无法匹配</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="str">
+      <x:c r="E12" s="62" t="str">
         <x:v>材料文件未匹配到订单或材料规则，已进入异常文件清单。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="16" t="str">
+      <x:c r="A13" s="62" t="str">
         <x:v>失败文案规范</x:v>
       </x:c>
-      <x:c r="B13" s="16" t="str">
+      <x:c r="B13" s="62" t="str">
         <x:v>订单级字段格式与金额异常按统一格式输出，便于运营定位Excel列</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="str">
+      <x:c r="C13" s="62" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="str">
+      <x:c r="D13" s="62" t="str">
         <x:v>字段名+字段格式错误；字段名+金额异常</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="str">
+      <x:c r="E13" s="62" t="str">
         <x:v>字段格式错误：字段名+字段格式错误；金额异常：字段名+金额异常</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="16" t="str">
+      <x:c r="A14" s="62" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="B14" s="16" t="str">
+      <x:c r="B14" s="62" t="str">
         <x:v>任务创建后，异步解析、校验或落库发生技术异常；按订单维度处理</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="str">
+      <x:c r="C14" s="62" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="str">
+      <x:c r="D14" s="62" t="str">
         <x:v>提示“系统异常”；整批订单均导入失败时批次状态为导入失败，存在成功订单时批次状态为导入完成，导入结果明细按订单维度展示导入结果</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="str">
+      <x:c r="E14" s="62" t="str">
         <x:v>系统异常</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="48" t="str">
+      <x:c r="A15" s="66" t="str">
         <x:v>覆盖成功口径</x:v>
       </x:c>
-      <x:c r="B15" s="48" t="str">
+      <x:c r="B15" s="66" t="str">
         <x:v>同批次订单未分配且未流转时自动覆盖。</x:v>
       </x:c>
-      <x:c r="C15" s="48" t="str">
+      <x:c r="C15" s="66" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D15" s="48" t="str">
+      <x:c r="D15" s="66" t="str">
         <x:v>同批次覆盖成功</x:v>
       </x:c>
-      <x:c r="E15" s="48" t="str">
+      <x:c r="E15" s="66" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；普通导入的处理结果为“成功”。同批次覆盖时，处理结果为“同批次覆盖成功：使用后传Excel字段覆盖已有订单”。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="48" t="str">
+      <x:c r="A16" s="66" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="B16" s="48" t="str">
+      <x:c r="B16" s="66" t="str">
         <x:v>本次同时导入主订单和续租订单，系统中已存在对应主子订单案件且均未流转。</x:v>
       </x:c>
-      <x:c r="C16" s="48" t="str">
+      <x:c r="C16" s="66" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D16" s="48" t="str">
+      <x:c r="D16" s="66" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="E16" s="48" t="str">
+      <x:c r="E16" s="66" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；处理结果为“主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新”。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="53" t="str">
+      <x:c r="A17" s="67" t="str">
         <x:v>最终结果保留口径</x:v>
       </x:c>
-      <x:c r="B17" s="53" t="str">
+      <x:c r="B17" s="67" t="str">
         <x:v>订单已为导入成功且待材料激活，后续再次上传Excel但本次字段校验失败。</x:v>
       </x:c>
-      <x:c r="C17" s="53" t="str">
+      <x:c r="C17" s="67" t="str">
         <x:v>本次记录失败；不覆盖订单最终结果</x:v>
       </x:c>
-      <x:c r="D17" s="53" t="str">
+      <x:c r="D17" s="67" t="str">
         <x:v>下载明细仍为导入成功 / 待材料激活 / 待补必填</x:v>
       </x:c>
-      <x:c r="E17" s="53" t="str">
+      <x:c r="E17" s="67" t="str">
         <x:v>本次Excel失败写入批次处理记录；下载明细按订单当前最终结果展示，处理结果保留当前缺失材料说明。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd33b182ea34fd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e480efee4cd4bf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2738,196 +2772,196 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="13" t="str">
+      <x:c r="A2" s="60" t="str">
         <x:v>适用范围</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
+      <x:c r="B2" s="60" t="str">
         <x:v>本明细用于二期案件导入及一期历史批次补充材料后的结果排查。</x:v>
       </x:c>
-      <x:c r="C2" s="13" t="str">
+      <x:c r="C2" s="60" t="str">
         <x:v>一期已生效案件不回退；二期在原有案件基础上补齐材料处理能力。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="60" t="str">
         <x:v>导入规则</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="60" t="str">
         <x:v>导入字段、必填项和材料要求均以选中的导入规则为准。</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="str">
+      <x:c r="C3" s="60" t="str">
         <x:v>前端可查看规则详情；规则配置由后台维护，订单字段与材料规则按资产方、业务类型生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="13" t="str">
+      <x:c r="A4" s="60" t="str">
         <x:v>Excel上传校验</x:v>
       </x:c>
-      <x:c r="B4" s="13" t="str">
+      <x:c r="B4" s="60" t="str">
         <x:v>列头须与模板一致，列顺序可调整，额外列忽略；同一文件内订单编号重复时整份文件上传失败。</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
+      <x:c r="C4" s="60" t="str">
         <x:v>列头不一致、缺少模板列、文件超限或单文件重复订单均在上传阶段拦截，不创建导入任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="13" t="str">
+      <x:c r="A5" s="60" t="str">
         <x:v>点击导入校验</x:v>
       </x:c>
-      <x:c r="B5" s="13" t="str">
+      <x:c r="B5" s="60" t="str">
         <x:v>订单必填字段为空、订单编号为空、格式或金额不合法等，按订单维度校验。</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="str">
+      <x:c r="C5" s="60" t="str">
         <x:v>校验失败仅影响对应订单，其余订单继续处理；失败原因写入导入结果明细。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="13" t="str">
+      <x:c r="A6" s="60" t="str">
         <x:v>材料包上传</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B6" s="60" t="str">
         <x:v>新建二期批次须同时上传Excel和材料包；材料包仅支持zip。</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
+      <x:c r="C6" s="60" t="str">
         <x:v>未上传材料包或上传非zip格式时整批不能提交；材料包解析异常不影响其它订单的字段处理。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="13" t="str">
+      <x:c r="A7" s="60" t="str">
         <x:v>草稿与批次状态</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
+      <x:c r="B7" s="60" t="str">
         <x:v>本期不提供保存草稿；未提交页面取消后不创建批次。</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="str">
+      <x:c r="C7" s="60" t="str">
         <x:v>批次导入状态仅为导入中、导入完成、导入失败。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="13" t="str">
+      <x:c r="A8" s="60" t="str">
         <x:v>异步处理</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="str">
+      <x:c r="B8" s="60" t="str">
         <x:v>点击导入后创建异步任务，页面展示“导入中”；任务结束后进入导入完成或导入失败。</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="str">
+      <x:c r="C8" s="60" t="str">
         <x:v>确认提示后返回案件导入管理，可进入导入处理详情或下载明细查看处理结果。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="13" t="str">
+      <x:c r="A9" s="60" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="B9" s="13" t="str">
+      <x:c r="B9" s="60" t="str">
         <x:v>已生效：字段及必填材料均满足；待材料激活：字段通过但缺少必填材料；导入失败：订单字段或业务校验未通过。</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="str">
+      <x:c r="C9" s="60" t="str">
         <x:v>待材料激活订单补齐必填材料并解析通过后自动变更为已生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="13" t="str">
+      <x:c r="A10" s="60" t="str">
         <x:v>材料状态</x:v>
       </x:c>
-      <x:c r="B10" s="13" t="str">
+      <x:c r="B10" s="60" t="str">
         <x:v>材料齐全、待补必填、待补非必填、未生成四种状态；待补材料展示当前缺失材料名称。</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="str">
+      <x:c r="C10" s="60" t="str">
         <x:v>缺少非必填材料不影响案件生效；材料异常文件在“异常文件”中查看。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="16" t="str">
+      <x:c r="A11" s="62" t="str">
         <x:v>批量补传</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B11" s="62" t="str">
         <x:v>同一批次可分多次上传，每次订单Excel最多500条。</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="str">
+      <x:c r="C11" s="62" t="str">
         <x:v>支持新增订单及材料、失败订单重新导入、仅补缺失材料、仅补订单Excel；处理过程归集在原批次。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="16" t="str">
+      <x:c r="A12" s="62" t="str">
         <x:v>最终结果导出</x:v>
       </x:c>
-      <x:c r="B12" s="16" t="str">
+      <x:c r="B12" s="62" t="str">
         <x:v>下载明细按订单当前最终结果导出，不按最后一次上传动作覆盖既有结果。</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="str">
+      <x:c r="C12" s="62" t="str">
         <x:v>待材料激活订单后续Excel校验失败时，仍展示导入成功、待材料激活、待补必填；本次失败仅写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="16" t="str">
+      <x:c r="A13" s="62" t="str">
         <x:v>重复与覆盖</x:v>
       </x:c>
-      <x:c r="B13" s="16" t="str">
+      <x:c r="B13" s="62" t="str">
         <x:v>跨批次同一资产方订单不允许重复导入；同批次再次导入时按订单当前案件状态判断是否可覆盖。</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="str">
+      <x:c r="C13" s="62" t="str">
         <x:v>案件已流转的订单不可覆盖；未流转且满足条件的订单可使用新上传Excel字段更新。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="16" t="str">
+      <x:c r="A14" s="62" t="str">
         <x:v>主续订单</x:v>
       </x:c>
-      <x:c r="B14" s="16" t="str">
+      <x:c r="B14" s="62" t="str">
         <x:v>首次导入续租订单时，主订单须同批导入且为已结清状态；首次导入主订单后，不允许再导入对应续租订单。</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="str">
+      <x:c r="C14" s="62" t="str">
         <x:v>主子订单同批复导且案件均未流转时可更新；仅已有主订单或单独导入续租订单时按主续关系异常阻断。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="16" t="str">
+      <x:c r="A15" s="62" t="str">
         <x:v>历史批次补材</x:v>
       </x:c>
-      <x:c r="B15" s="16" t="str">
+      <x:c r="B15" s="62" t="str">
         <x:v>一期历史案件仅导入Excel，案件已生效；材料状态初始为待初始化（一期）。</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="str">
+      <x:c r="C15" s="62" t="str">
         <x:v>可通过补充历史材料上传ZIP材料包；解析后更新材料状态，不影响待委外及后续法诉流程。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="16" t="str">
+      <x:c r="A16" s="62" t="str">
         <x:v>下载明细</x:v>
       </x:c>
-      <x:c r="B16" s="16" t="str">
+      <x:c r="B16" s="62" t="str">
         <x:v>批次管理“下载明细”与导入处理详情“导出当前筛选订单明细”使用同一模板。</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="str">
+      <x:c r="C16" s="62" t="str">
         <x:v>工作簿包含导入结果明细、待补材料明细、失败分类说明、口径说明。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="16" t="str">
+      <x:c r="A17" s="62" t="str">
         <x:v>法诉材料导出</x:v>
       </x:c>
-      <x:c r="B17" s="16" t="str">
+      <x:c r="B17" s="62" t="str">
         <x:v>一期历史案件在未补齐材料前不支持导出法诉材料。</x:v>
       </x:c>
-      <x:c r="C17" s="16" t="str">
+      <x:c r="C17" s="62" t="str">
         <x:v>历史案件补充材料包且解析完成后，可在法诉系统现有功能中按既有能力导出法诉材料。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="16" t="str">
+      <x:c r="A18" s="62" t="str">
         <x:v>批次信息与附件</x:v>
       </x:c>
-      <x:c r="B18" s="16" t="str">
+      <x:c r="B18" s="62" t="str">
         <x:v>债权出让主体为文本输入，最多50字；附件用于留存债权转让协议、转账回单、补充协议等。</x:v>
       </x:c>
-      <x:c r="C18" s="16" t="str">
+      <x:c r="C18" s="62" t="str">
         <x:v>单批次最多10个附件，支持pdf、图片、xlsx、xls、zip；已上传附件支持下载、删除。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5591f23c7444879"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra92383a111154567"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2948,212 +2982,212 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="59" t="str">
+      <x:c r="A1" s="65" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="59" t="str">
+      <x:c r="B1" s="65" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="59" t="str">
+      <x:c r="C1" s="65" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="59" t="str">
+      <x:c r="D1" s="65" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="59" t="str">
+      <x:c r="E1" s="65" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="59" t="str">
+      <x:c r="F1" s="65" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="59" t="str">
+      <x:c r="G1" s="65" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="59" t="str">
+      <x:c r="H1" s="65" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="I1" s="59" t="str">
+      <x:c r="I1" s="65" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="18" t="str">
+      <x:c r="A2" s="63" t="str">
         <x:v>26012915050167612342</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="62" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="62" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="str">
+      <x:c r="D2" s="62" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E2" s="16" t="str">
+      <x:c r="E2" s="62" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="str">
+      <x:c r="F2" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G2" s="16" t="str">
+      <x:c r="G2" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H2" s="16" t="str">
+      <x:c r="H2" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="str">
+      <x:c r="I2" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="18" t="str">
+      <x:c r="A3" s="63" t="str">
         <x:v>26012915050167612343</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="str">
+      <x:c r="B3" s="62" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="str">
+      <x:c r="C3" s="62" t="str">
         <x:v>订单信息</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="str">
+      <x:c r="D3" s="62" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="E3" s="16" t="str">
+      <x:c r="E3" s="62" t="str">
         <x:v>非必填</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="str">
+      <x:c r="F3" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="G3" s="16" t="str">
+      <x:c r="G3" s="62" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="H3" s="16" t="str">
+      <x:c r="H3" s="62" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="I3" s="16" t="str">
+      <x:c r="I3" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="18" t="str">
+      <x:c r="A4" s="63" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="62" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="62" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="D4" s="62" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
+      <x:c r="E4" s="62" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="str">
+      <x:c r="F4" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="str">
+      <x:c r="G4" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H4" s="16" t="str">
+      <x:c r="H4" s="62" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="str">
+      <x:c r="I4" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="A5" s="63" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B5" s="62" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C5" s="62" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D5" s="62" t="str">
         <x:v>租赁服务合同验签报告</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
+      <x:c r="E5" s="62" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="str">
+      <x:c r="F5" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G5" s="16" t="str">
+      <x:c r="G5" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H5" s="16" t="str">
+      <x:c r="H5" s="62" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I5" s="16" t="str">
+      <x:c r="I5" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="18" t="str">
+      <x:c r="A6" s="63" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
+      <x:c r="B6" s="62" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C6" s="16" t="str">
+      <x:c r="C6" s="62" t="str">
         <x:v>订单信息</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="str">
+      <x:c r="D6" s="62" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="str">
+      <x:c r="E6" s="62" t="str">
         <x:v>非必填</x:v>
       </x:c>
-      <x:c r="F6" s="16" t="str">
+      <x:c r="F6" s="62" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G6" s="16" t="str">
+      <x:c r="G6" s="62" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="H6" s="16" t="str">
+      <x:c r="H6" s="62" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I6" s="16" t="str">
+      <x:c r="I6" s="62" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="A7" s="63" t="str">
         <x:v>26012915050167612001</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" s="62" t="str">
         <x:v>吴静</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="str">
+      <x:c r="C7" s="62" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="str">
+      <x:c r="D7" s="62" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="str">
+      <x:c r="E7" s="62" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="str">
+      <x:c r="F7" s="62" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="str">
+      <x:c r="G7" s="62" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H7" s="16" t="str">
+      <x:c r="H7" s="62" t="str">
         <x:v>2026-06-12 10:15:26</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="str">
+      <x:c r="I7" s="62" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd80f80dbcbba41eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78f86adacd44478c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/法诉案件导入_导入结果明细.xlsx
+++ b/法诉案件导入_导入结果明细.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R47bf201c01ab44cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="R83fe00a579794bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R0f3b62c7a34b491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="Rf1ece1d490324794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入结果明细" sheetId="1" r:id="R3e60dbf509de4a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败分类说明" sheetId="2" r:id="Rc3f4c9e1163544cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R184ff3f7156e404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补材料明细" sheetId="4" r:id="R0f65f53cfe7c49cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="53">
+  <x:fills count="55">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -411,6 +411,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F4F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -703,7 +713,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="80">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -888,6 +898,42 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="51" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="24" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="25" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="54" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="54" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="53" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1127,7 +1173,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="Table1" displayName="Table1" ref="A1:R18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="导入批次号"/>
     <x:tableColumn id="2" name="批次名称"/>
@@ -1177,7 +1223,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="Table4" displayName="Table4" ref="A1:I7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="订单编号"/>
     <x:tableColumn id="2" name="客户姓名"/>
@@ -1448,931 +1494,931 @@
       <x:c r="M1" s="8" t="str">
         <x:v>失败字段</x:v>
       </x:c>
-      <x:c r="N1" s="64" t="str">
+      <x:c r="N1" s="74" t="str">
         <x:v>字段值</x:v>
       </x:c>
-      <x:c r="O1" s="65" t="str">
+      <x:c r="O1" s="75" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="P1" s="65" t="str">
+      <x:c r="P1" s="75" t="str">
         <x:v>是否阻断导入</x:v>
       </x:c>
-      <x:c r="Q1" s="65" t="str">
+      <x:c r="Q1" s="75" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="R1" s="65" t="str">
+      <x:c r="R1" s="75" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="60" t="str">
+      <x:c r="A2" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B2" s="60" t="str">
+      <x:c r="B2" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C2" s="60" t="str">
+      <x:c r="C2" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D2" s="60" t="str">
+      <x:c r="D2" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E2" s="61" t="str">
+      <x:c r="E2" s="71" t="str">
         <x:v>26012915050167612327</x:v>
       </x:c>
-      <x:c r="F2" s="61" t="str">
+      <x:c r="F2" s="71" t="str">
         <x:v>张三</x:v>
       </x:c>
-      <x:c r="G2" s="61" t="str">
+      <x:c r="G2" s="71" t="str">
         <x:v>420106199201018888</x:v>
       </x:c>
-      <x:c r="H2" s="60" t="str">
+      <x:c r="H2" s="70" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="str">
+      <x:c r="I2" s="70" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J2" s="60" t="str">
+      <x:c r="J2" s="70" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K2" s="60" t="str">
+      <x:c r="K2" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L2" s="60" t="str"/>
-      <x:c r="M2" s="60" t="str"/>
-      <x:c r="N2" s="60" t="str"/>
-      <x:c r="O2" s="62" t="str">
+      <x:c r="L2" s="70" t="str"/>
+      <x:c r="M2" s="70" t="str"/>
+      <x:c r="N2" s="70" t="str"/>
+      <x:c r="O2" s="72" t="str">
         <x:v>成功</x:v>
       </x:c>
-      <x:c r="P2" s="62" t="str">
+      <x:c r="P2" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q2" s="62" t="str">
+      <x:c r="Q2" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R2" s="62" t="str">
+      <x:c r="R2" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="60" t="str">
+      <x:c r="A3" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B3" s="60" t="str">
+      <x:c r="B3" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C3" s="60" t="str">
+      <x:c r="C3" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D3" s="60" t="str">
+      <x:c r="D3" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E3" s="61" t="str">
+      <x:c r="E3" s="71" t="str">
         <x:v>26012915050167612328</x:v>
       </x:c>
-      <x:c r="F3" s="61" t="str">
+      <x:c r="F3" s="71" t="str">
         <x:v>李明</x:v>
       </x:c>
-      <x:c r="G3" s="61" t="str">
+      <x:c r="G3" s="71" t="str">
         <x:v>420106199201019999</x:v>
       </x:c>
-      <x:c r="H3" s="60" t="str">
+      <x:c r="H3" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I3" s="60" t="str">
+      <x:c r="I3" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J3" s="60" t="str">
+      <x:c r="J3" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K3" s="60" t="str">
+      <x:c r="K3" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="str">
+      <x:c r="L3" s="70" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="str">
+      <x:c r="M3" s="70" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="N3" s="60" t="str"/>
-      <x:c r="O3" s="62" t="str">
+      <x:c r="N3" s="70" t="str"/>
+      <x:c r="O3" s="72" t="str">
         <x:v>债权金额为必填字段，当前为空</x:v>
       </x:c>
-      <x:c r="P3" s="62" t="str">
+      <x:c r="P3" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q3" s="62" t="str">
+      <x:c r="Q3" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R3" s="62" t="str">
+      <x:c r="R3" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="60" t="str">
+      <x:c r="A4" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B4" s="60" t="str">
+      <x:c r="B4" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C4" s="60" t="str">
+      <x:c r="C4" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D4" s="60" t="str">
+      <x:c r="D4" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E4" s="61" t="str">
+      <x:c r="E4" s="71" t="str">
         <x:v>26012915050167612329</x:v>
       </x:c>
-      <x:c r="F4" s="61" t="str">
+      <x:c r="F4" s="71" t="str">
         <x:v>王磊</x:v>
       </x:c>
-      <x:c r="G4" s="61" t="str">
+      <x:c r="G4" s="71" t="str">
         <x:v>42010619920101</x:v>
       </x:c>
-      <x:c r="H4" s="60" t="str">
+      <x:c r="H4" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I4" s="60" t="str">
+      <x:c r="I4" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J4" s="60" t="str">
+      <x:c r="J4" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K4" s="60" t="str">
+      <x:c r="K4" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L4" s="60" t="str">
+      <x:c r="L4" s="70" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="M4" s="60" t="str">
+      <x:c r="M4" s="70" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="N4" s="60" t="str">
+      <x:c r="N4" s="70" t="str">
         <x:v>42010619920101</x:v>
       </x:c>
-      <x:c r="O4" s="62" t="str">
+      <x:c r="O4" s="72" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-      <x:c r="P4" s="62" t="str">
+      <x:c r="P4" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q4" s="62" t="str">
+      <x:c r="Q4" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R4" s="62" t="str">
+      <x:c r="R4" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="60" t="str">
+      <x:c r="A5" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B5" s="60" t="str">
+      <x:c r="B5" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C5" s="60" t="str">
+      <x:c r="C5" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D5" s="60" t="str">
+      <x:c r="D5" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E5" s="61" t="str">
+      <x:c r="E5" s="71" t="str">
         <x:v>26012915050167612330</x:v>
       </x:c>
-      <x:c r="F5" s="61" t="str">
+      <x:c r="F5" s="71" t="str">
         <x:v>黄丽</x:v>
       </x:c>
-      <x:c r="G5" s="61" t="str">
+      <x:c r="G5" s="71" t="str">
         <x:v>420106199201017777</x:v>
       </x:c>
-      <x:c r="H5" s="60" t="str">
+      <x:c r="H5" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I5" s="60" t="str">
+      <x:c r="I5" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J5" s="60" t="str">
+      <x:c r="J5" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K5" s="60" t="str">
+      <x:c r="K5" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L5" s="60" t="str">
+      <x:c r="L5" s="70" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="M5" s="60" t="str">
+      <x:c r="M5" s="70" t="str">
         <x:v>债权金额</x:v>
       </x:c>
-      <x:c r="N5" s="60" t="str">
+      <x:c r="N5" s="70" t="str">
         <x:v>-5999.00</x:v>
       </x:c>
-      <x:c r="O5" s="62" t="str">
+      <x:c r="O5" s="72" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-      <x:c r="P5" s="62" t="str">
+      <x:c r="P5" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q5" s="62" t="str">
+      <x:c r="Q5" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R5" s="62" t="str">
+      <x:c r="R5" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="60" t="str">
+      <x:c r="A6" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B6" s="60" t="str">
+      <x:c r="B6" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C6" s="60" t="str">
+      <x:c r="C6" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D6" s="60" t="str">
+      <x:c r="D6" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E6" s="61" t="str">
+      <x:c r="E6" s="71" t="str">
         <x:v>26012915050167612331</x:v>
       </x:c>
-      <x:c r="F6" s="61" t="str">
+      <x:c r="F6" s="71" t="str">
         <x:v>周强</x:v>
       </x:c>
-      <x:c r="G6" s="61" t="str">
+      <x:c r="G6" s="71" t="str">
         <x:v>420106199201016666</x:v>
       </x:c>
-      <x:c r="H6" s="60" t="str">
+      <x:c r="H6" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I6" s="60" t="str">
+      <x:c r="I6" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J6" s="60" t="str">
+      <x:c r="J6" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K6" s="60" t="str">
+      <x:c r="K6" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L6" s="60" t="str">
+      <x:c r="L6" s="70" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="M6" s="60" t="str">
+      <x:c r="M6" s="70" t="str">
         <x:v>性别</x:v>
       </x:c>
-      <x:c r="N6" s="60" t="str">
+      <x:c r="N6" s="70" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="O6" s="62" t="str">
+      <x:c r="O6" s="72" t="str">
         <x:v>性别字段格式错误</x:v>
       </x:c>
-      <x:c r="P6" s="62" t="str">
+      <x:c r="P6" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q6" s="62" t="str">
+      <x:c r="Q6" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R6" s="62" t="str">
+      <x:c r="R6" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="60" t="str">
+      <x:c r="A7" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B7" s="60" t="str">
+      <x:c r="B7" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C7" s="60" t="str">
+      <x:c r="C7" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D7" s="60" t="str">
+      <x:c r="D7" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E7" s="61" t="str">
+      <x:c r="E7" s="71" t="str">
         <x:v>26012915050167612332</x:v>
       </x:c>
-      <x:c r="F7" s="61" t="str">
+      <x:c r="F7" s="71" t="str">
         <x:v>赵倩</x:v>
       </x:c>
-      <x:c r="G7" s="61" t="str">
+      <x:c r="G7" s="71" t="str">
         <x:v>420106199201015555</x:v>
       </x:c>
-      <x:c r="H7" s="60" t="str">
+      <x:c r="H7" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I7" s="60" t="str">
+      <x:c r="I7" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J7" s="60" t="str">
+      <x:c r="J7" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K7" s="60" t="str">
+      <x:c r="K7" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L7" s="60" t="str">
+      <x:c r="L7" s="70" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M7" s="60" t="str">
+      <x:c r="M7" s="70" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="N7" s="60" t="str">
+      <x:c r="N7" s="70" t="str">
         <x:v>26012915050167610001</x:v>
       </x:c>
-      <x:c r="O7" s="62" t="str">
+      <x:c r="O7" s="72" t="str">
         <x:v>父订单编号不存在，且本批次未导入对应主订单</x:v>
       </x:c>
-      <x:c r="P7" s="62" t="str">
+      <x:c r="P7" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q7" s="62" t="str">
+      <x:c r="Q7" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R7" s="62" t="str">
+      <x:c r="R7" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="60" t="str">
+      <x:c r="A8" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B8" s="60" t="str">
+      <x:c r="B8" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C8" s="60" t="str">
+      <x:c r="C8" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D8" s="60" t="str">
+      <x:c r="D8" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E8" s="61" t="str">
+      <x:c r="E8" s="71" t="str">
         <x:v>26012915050167612336</x:v>
       </x:c>
-      <x:c r="F8" s="61" t="str">
+      <x:c r="F8" s="71" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="G8" s="61" t="str">
+      <x:c r="G8" s="71" t="str">
         <x:v>420106199201010001</x:v>
       </x:c>
-      <x:c r="H8" s="60" t="str">
+      <x:c r="H8" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I8" s="60" t="str">
+      <x:c r="I8" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J8" s="60" t="str">
+      <x:c r="J8" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K8" s="60" t="str">
+      <x:c r="K8" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L8" s="60" t="str">
+      <x:c r="L8" s="70" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M8" s="60" t="str">
+      <x:c r="M8" s="70" t="str">
         <x:v>身份证号</x:v>
       </x:c>
-      <x:c r="N8" s="60" t="str">
+      <x:c r="N8" s="70" t="str">
         <x:v>420106199201010001</x:v>
       </x:c>
-      <x:c r="O8" s="62" t="str">
+      <x:c r="O8" s="72" t="str">
         <x:v>父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。</x:v>
       </x:c>
-      <x:c r="P8" s="62" t="str">
+      <x:c r="P8" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q8" s="62" t="str">
+      <x:c r="Q8" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R8" s="62" t="str">
+      <x:c r="R8" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="60" t="str">
+      <x:c r="A9" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B9" s="60" t="str">
+      <x:c r="B9" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C9" s="60" t="str">
+      <x:c r="C9" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D9" s="60" t="str">
+      <x:c r="D9" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E9" s="61" t="str">
+      <x:c r="E9" s="71" t="str">
         <x:v>26012915050167612337</x:v>
       </x:c>
-      <x:c r="F9" s="61" t="str">
+      <x:c r="F9" s="71" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G9" s="61" t="str">
+      <x:c r="G9" s="71" t="str">
         <x:v>420106199201010002</x:v>
       </x:c>
-      <x:c r="H9" s="60" t="str">
+      <x:c r="H9" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I9" s="60" t="str">
+      <x:c r="I9" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J9" s="60" t="str">
+      <x:c r="J9" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K9" s="60" t="str">
+      <x:c r="K9" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L9" s="60" t="str">
+      <x:c r="L9" s="70" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="M9" s="60" t="str">
+      <x:c r="M9" s="70" t="str">
         <x:v>违约日</x:v>
       </x:c>
-      <x:c r="N9" s="60" t="str"/>
-      <x:c r="O9" s="62" t="str">
+      <x:c r="N9" s="70" t="str"/>
+      <x:c r="O9" s="72" t="str">
         <x:v>续租订单违约日不能为空，请补充后重新上传。</x:v>
       </x:c>
-      <x:c r="P9" s="62" t="str">
+      <x:c r="P9" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q9" s="62" t="str">
+      <x:c r="Q9" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R9" s="62" t="str">
+      <x:c r="R9" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="60" t="str">
+      <x:c r="A10" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B10" s="60" t="str">
+      <x:c r="B10" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C10" s="60" t="str">
+      <x:c r="C10" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D10" s="60" t="str">
+      <x:c r="D10" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E10" s="61" t="str">
+      <x:c r="E10" s="71" t="str">
         <x:v>26012915050167612333</x:v>
       </x:c>
-      <x:c r="F10" s="61" t="str">
+      <x:c r="F10" s="71" t="str">
         <x:v>陈晨</x:v>
       </x:c>
-      <x:c r="G10" s="61" t="str">
+      <x:c r="G10" s="71" t="str">
         <x:v>420106199201014444</x:v>
       </x:c>
-      <x:c r="H10" s="60" t="str">
+      <x:c r="H10" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I10" s="60" t="str">
+      <x:c r="I10" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J10" s="60" t="str">
+      <x:c r="J10" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K10" s="60" t="str">
+      <x:c r="K10" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L10" s="60" t="str">
+      <x:c r="L10" s="70" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="M10" s="60" t="str">
+      <x:c r="M10" s="70" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="N10" s="60" t="str">
+      <x:c r="N10" s="70" t="str">
         <x:v>26012915050167612333</x:v>
       </x:c>
-      <x:c r="O10" s="62" t="str">
+      <x:c r="O10" s="72" t="str">
         <x:v>该订单已在批次DR202606100001导入，本次不允许重复导入</x:v>
       </x:c>
-      <x:c r="P10" s="62" t="str">
+      <x:c r="P10" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q10" s="62" t="str">
+      <x:c r="Q10" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R10" s="62" t="str">
+      <x:c r="R10" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="60" t="str">
+      <x:c r="A11" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B11" s="60" t="str">
+      <x:c r="B11" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C11" s="60" t="str">
+      <x:c r="C11" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D11" s="60" t="str">
+      <x:c r="D11" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E11" s="61" t="str">
+      <x:c r="E11" s="71" t="str">
         <x:v>26012915050167612340</x:v>
       </x:c>
-      <x:c r="F11" s="61" t="str">
+      <x:c r="F11" s="71" t="str">
         <x:v>刘洋</x:v>
       </x:c>
-      <x:c r="G11" s="61" t="str">
+      <x:c r="G11" s="71" t="str">
         <x:v>420106199201010003</x:v>
       </x:c>
-      <x:c r="H11" s="60" t="str">
+      <x:c r="H11" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I11" s="60" t="str">
+      <x:c r="I11" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J11" s="60" t="str">
+      <x:c r="J11" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K11" s="60" t="str">
+      <x:c r="K11" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L11" s="60" t="str">
+      <x:c r="L11" s="70" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="M11" s="60" t="str">
+      <x:c r="M11" s="70" t="str">
         <x:v>父订单编号</x:v>
       </x:c>
-      <x:c r="N11" s="60" t="str">
+      <x:c r="N11" s="70" t="str">
         <x:v>26012915050167612327</x:v>
       </x:c>
-      <x:c r="O11" s="62" t="str">
+      <x:c r="O11" s="72" t="str">
         <x:v>续租订单关联的主订单【26012915050167612327】已在法诉系统形成案件，不符合续租订单导入条件。</x:v>
       </x:c>
-      <x:c r="P11" s="62" t="str">
+      <x:c r="P11" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q11" s="62" t="str">
+      <x:c r="Q11" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R11" s="62" t="str">
+      <x:c r="R11" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="60" t="str">
+      <x:c r="A12" s="70" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B12" s="60" t="str">
+      <x:c r="B12" s="70" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C12" s="60" t="str">
+      <x:c r="C12" s="70" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D12" s="60" t="str">
+      <x:c r="D12" s="70" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E12" s="61" t="str">
+      <x:c r="E12" s="71" t="str">
         <x:v>26012915050167612341</x:v>
       </x:c>
-      <x:c r="F12" s="61" t="str">
+      <x:c r="F12" s="71" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="G12" s="61" t="str">
+      <x:c r="G12" s="71" t="str">
         <x:v>420106199201010004</x:v>
       </x:c>
-      <x:c r="H12" s="60" t="str">
+      <x:c r="H12" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="I12" s="60" t="str">
+      <x:c r="I12" s="70" t="str">
         <x:v>导入失败</x:v>
       </x:c>
-      <x:c r="J12" s="60" t="str">
+      <x:c r="J12" s="70" t="str">
         <x:v>未生成</x:v>
       </x:c>
-      <x:c r="K12" s="60" t="str">
+      <x:c r="K12" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L12" s="60" t="str">
+      <x:c r="L12" s="70" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="M12" s="60" t="str">
+      <x:c r="M12" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="N12" s="60" t="str">
+      <x:c r="N12" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="O12" s="62" t="str">
+      <x:c r="O12" s="72" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="P12" s="62" t="str">
+      <x:c r="P12" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="Q12" s="62" t="str">
+      <x:c r="Q12" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R12" s="62" t="str">
+      <x:c r="R12" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
-      <x:c r="A13" s="62" t="str">
+      <x:c r="A13" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B13" s="62" t="str">
+      <x:c r="B13" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C13" s="62" t="str">
+      <x:c r="C13" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D13" s="62" t="str">
+      <x:c r="D13" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E13" s="63" t="str">
+      <x:c r="E13" s="73" t="str">
         <x:v>26012915050167612342</x:v>
       </x:c>
-      <x:c r="F13" s="63" t="str">
+      <x:c r="F13" s="73" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="G13" s="63" t="str">
+      <x:c r="G13" s="73" t="str">
         <x:v>420106199201010005</x:v>
       </x:c>
-      <x:c r="H13" s="62" t="str">
+      <x:c r="H13" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I13" s="62" t="str">
+      <x:c r="I13" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="J13" s="62" t="str">
+      <x:c r="J13" s="72" t="str">
         <x:v>待补必填</x:v>
       </x:c>
-      <x:c r="K13" s="62" t="str">
+      <x:c r="K13" s="72" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="L13" s="62" t="str">
+      <x:c r="L13" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M13" s="62" t="str"/>
-      <x:c r="N13" s="62" t="str"/>
-      <x:c r="O13" s="62" t="str">
+      <x:c r="M13" s="72" t="str"/>
+      <x:c r="N13" s="72" t="str"/>
+      <x:c r="O13" s="72" t="str">
         <x:v>字段校验通过，缺少必填材料：租赁服务合同。</x:v>
       </x:c>
-      <x:c r="P13" s="62" t="str">
+      <x:c r="P13" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q13" s="62" t="str">
+      <x:c r="Q13" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R13" s="62" t="str">
+      <x:c r="R13" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="62" t="str">
+      <x:c r="A14" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B14" s="62" t="str">
+      <x:c r="B14" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C14" s="62" t="str">
+      <x:c r="C14" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D14" s="62" t="str">
+      <x:c r="D14" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E14" s="63" t="str">
+      <x:c r="E14" s="73" t="str">
         <x:v>26012915050167612343</x:v>
       </x:c>
-      <x:c r="F14" s="63" t="str">
+      <x:c r="F14" s="73" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="G14" s="63" t="str">
+      <x:c r="G14" s="73" t="str">
         <x:v>420106199201010006</x:v>
       </x:c>
-      <x:c r="H14" s="62" t="str">
+      <x:c r="H14" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I14" s="62" t="str">
+      <x:c r="I14" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J14" s="62" t="str">
+      <x:c r="J14" s="72" t="str">
         <x:v>待补非必填</x:v>
       </x:c>
-      <x:c r="K14" s="62" t="str">
+      <x:c r="K14" s="72" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="L14" s="62" t="str">
+      <x:c r="L14" s="72" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="M14" s="62" t="str"/>
-      <x:c r="N14" s="62" t="str"/>
-      <x:c r="O14" s="62" t="str">
+      <x:c r="M14" s="72" t="str"/>
+      <x:c r="N14" s="72" t="str"/>
+      <x:c r="O14" s="72" t="str">
         <x:v>字段校验通过，缺少非必填材料：订单详情-物流。</x:v>
       </x:c>
-      <x:c r="P14" s="62" t="str">
+      <x:c r="P14" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q14" s="62" t="str">
+      <x:c r="Q14" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="R14" s="62" t="str">
+      <x:c r="R14" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="62" t="str">
+      <x:c r="A15" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B15" s="62" t="str">
+      <x:c r="B15" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C15" s="62" t="str">
+      <x:c r="C15" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D15" s="62" t="str">
+      <x:c r="D15" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E15" s="63" t="str">
+      <x:c r="E15" s="73" t="str">
         <x:v>26012915050167612344</x:v>
       </x:c>
-      <x:c r="F15" s="63" t="str">
+      <x:c r="F15" s="73" t="str">
         <x:v>许诺</x:v>
       </x:c>
-      <x:c r="G15" s="63" t="str">
+      <x:c r="G15" s="73" t="str">
         <x:v>420106199201010007</x:v>
       </x:c>
-      <x:c r="H15" s="62" t="str">
+      <x:c r="H15" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I15" s="62" t="str">
+      <x:c r="I15" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J15" s="62" t="str">
+      <x:c r="J15" s="72" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K15" s="62" t="str">
+      <x:c r="K15" s="72" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L15" s="62" t="str"/>
-      <x:c r="M15" s="62" t="str"/>
-      <x:c r="N15" s="62" t="str"/>
-      <x:c r="O15" s="62" t="str">
+      <x:c r="L15" s="72" t="str"/>
+      <x:c r="M15" s="72" t="str"/>
+      <x:c r="N15" s="72" t="str"/>
+      <x:c r="O15" s="72" t="str">
         <x:v>同批次覆盖成功：使用后传Excel字段覆盖已有订单。</x:v>
       </x:c>
-      <x:c r="P15" s="62" t="str">
+      <x:c r="P15" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q15" s="62" t="str">
+      <x:c r="Q15" s="72" t="str">
         <x:v>2026-06-12 10:05:18</x:v>
       </x:c>
-      <x:c r="R15" s="62" t="str">
+      <x:c r="R15" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
-      <x:c r="A16" s="62" t="str">
+      <x:c r="A16" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B16" s="62" t="str">
+      <x:c r="B16" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C16" s="62" t="str">
+      <x:c r="C16" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D16" s="62" t="str">
+      <x:c r="D16" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E16" s="63" t="str">
+      <x:c r="E16" s="73" t="str">
         <x:v>26012915050167612345</x:v>
       </x:c>
-      <x:c r="F16" s="63" t="str">
+      <x:c r="F16" s="73" t="str">
         <x:v>周薇</x:v>
       </x:c>
-      <x:c r="G16" s="63" t="str">
+      <x:c r="G16" s="73" t="str">
         <x:v>420106199201010008</x:v>
       </x:c>
-      <x:c r="H16" s="62" t="str">
+      <x:c r="H16" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I16" s="62" t="str">
+      <x:c r="I16" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J16" s="62" t="str">
+      <x:c r="J16" s="72" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K16" s="62" t="str">
+      <x:c r="K16" s="72" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L16" s="62" t="str"/>
-      <x:c r="M16" s="62" t="str"/>
-      <x:c r="N16" s="62" t="str"/>
-      <x:c r="O16" s="62" t="str">
+      <x:c r="L16" s="72" t="str"/>
+      <x:c r="M16" s="72" t="str"/>
+      <x:c r="N16" s="72" t="str"/>
+      <x:c r="O16" s="72" t="str">
         <x:v>重复跳过：该订单已分配或已流转，不可覆盖。</x:v>
       </x:c>
-      <x:c r="P16" s="62" t="str">
+      <x:c r="P16" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q16" s="62" t="str">
+      <x:c r="Q16" s="72" t="str">
         <x:v>2026-06-12 10:06:42</x:v>
       </x:c>
-      <x:c r="R16" s="62" t="str">
+      <x:c r="R16" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
-      <x:c r="A17" s="62" t="str">
+      <x:c r="A17" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B17" s="62" t="str">
+      <x:c r="B17" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C17" s="62" t="str">
+      <x:c r="C17" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D17" s="62" t="str">
+      <x:c r="D17" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E17" s="63" t="str">
+      <x:c r="E17" s="73" t="str">
         <x:v>26012915050167612347</x:v>
       </x:c>
-      <x:c r="F17" s="63" t="str">
+      <x:c r="F17" s="73" t="str">
         <x:v>郑楠</x:v>
       </x:c>
-      <x:c r="G17" s="63" t="str">
+      <x:c r="G17" s="73" t="str">
         <x:v>420106199201010010</x:v>
       </x:c>
-      <x:c r="H17" s="62" t="str">
+      <x:c r="H17" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I17" s="62" t="str">
+      <x:c r="I17" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="J17" s="62" t="str">
+      <x:c r="J17" s="72" t="str">
         <x:v>材料齐全</x:v>
       </x:c>
-      <x:c r="K17" s="62" t="str">
+      <x:c r="K17" s="72" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="L17" s="62" t="str"/>
-      <x:c r="M17" s="62" t="str"/>
-      <x:c r="N17" s="62" t="str"/>
-      <x:c r="O17" s="62" t="str">
+      <x:c r="L17" s="72" t="str"/>
+      <x:c r="M17" s="72" t="str"/>
+      <x:c r="N17" s="72" t="str"/>
+      <x:c r="O17" s="72" t="str">
         <x:v>主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新。</x:v>
       </x:c>
-      <x:c r="P17" s="62" t="str">
+      <x:c r="P17" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q17" s="62" t="str">
+      <x:c r="Q17" s="72" t="str">
         <x:v>2026-06-12 10:10:34</x:v>
       </x:c>
-      <x:c r="R17" s="62" t="str">
+      <x:c r="R17" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
-      <x:c r="A18" s="62" t="str">
+      <x:c r="A18" s="72" t="str">
         <x:v>DR202606120003</x:v>
       </x:c>
-      <x:c r="B18" s="62" t="str">
+      <x:c r="B18" s="72" t="str">
         <x:v>创新租赁一期Excel导入批次04</x:v>
       </x:c>
-      <x:c r="C18" s="62" t="str">
+      <x:c r="C18" s="72" t="str">
         <x:v>创新</x:v>
       </x:c>
-      <x:c r="D18" s="62" t="str">
+      <x:c r="D18" s="72" t="str">
         <x:v>租赁</x:v>
       </x:c>
-      <x:c r="E18" s="63" t="str">
+      <x:c r="E18" s="73" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="F18" s="63" t="str">
+      <x:c r="F18" s="73" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="G18" s="63" t="str">
+      <x:c r="G18" s="73" t="str">
         <x:v>420106199201010011</x:v>
       </x:c>
-      <x:c r="H18" s="62" t="str">
+      <x:c r="H18" s="72" t="str">
         <x:v>导入成功</x:v>
       </x:c>
-      <x:c r="I18" s="62" t="str">
+      <x:c r="I18" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="J18" s="62" t="str">
+      <x:c r="J18" s="72" t="str">
         <x:v>待补必填</x:v>
       </x:c>
-      <x:c r="K18" s="62" t="str">
+      <x:c r="K18" s="72" t="str">
         <x:v>租赁服务合同；租赁服务合同验签报告</x:v>
       </x:c>
-      <x:c r="L18" s="62" t="str">
+      <x:c r="L18" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="M18" s="62" t="str"/>
-      <x:c r="N18" s="62" t="str"/>
-      <x:c r="O18" s="62" t="str">
+      <x:c r="M18" s="72" t="str"/>
+      <x:c r="N18" s="72" t="str"/>
+      <x:c r="O18" s="72" t="str">
         <x:v>字段校验通过，缺少必填材料：租赁服务合同；租赁服务合同验签报告。</x:v>
       </x:c>
-      <x:c r="P18" s="62" t="str">
+      <x:c r="P18" s="72" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q18" s="62" t="str">
+      <x:c r="Q18" s="72" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="R18" s="62" t="str">
+      <x:c r="R18" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
@@ -2429,7 +2475,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39b181e0a0234731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ede666174544301"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2463,19 +2509,19 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="60" t="str">
+      <x:c r="A2" s="70" t="str">
         <x:v>文件级前置校验</x:v>
       </x:c>
-      <x:c r="B2" s="60" t="str">
+      <x:c r="B2" s="70" t="str">
         <x:v>订单编号为空、同一Excel订单编号重复、必填列缺失、重复列头、文件超过50MB、订单超过500条</x:v>
       </x:c>
-      <x:c r="C2" s="60" t="str">
+      <x:c r="C2" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D2" s="60" t="str">
+      <x:c r="D2" s="70" t="str">
         <x:v>模板中有重复订单，请修正后重新上传。</x:v>
       </x:c>
-      <x:c r="E2" s="60" t="str">
+      <x:c r="E2" s="70" t="str">
         <x:v>订单编号为空：模板中订单编号不能为空，请修正后重新上传。
 重复订单：模板中有重复订单，请修正后重新上传。
 文件超过50MB：上传文件超过50MB，请压缩或拆分后重新上传。
@@ -2483,106 +2529,106 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
-      <x:c r="A3" s="60" t="str">
+      <x:c r="A3" s="70" t="str">
         <x:v>模板格式错误</x:v>
       </x:c>
-      <x:c r="B3" s="60" t="str">
+      <x:c r="B3" s="70" t="str">
         <x:v>文件无法解析、列头名称与模板不一致、缺少必填列等模板问题</x:v>
       </x:c>
-      <x:c r="C3" s="60" t="str">
+      <x:c r="C3" s="70" t="str">
         <x:v>上传阶段拦截</x:v>
       </x:c>
-      <x:c r="D3" s="60" t="str">
+      <x:c r="D3" s="70" t="str">
         <x:v>整份文件上传失败，不创建任务</x:v>
       </x:c>
-      <x:c r="E3" s="60" t="str">
+      <x:c r="E3" s="70" t="str">
         <x:v>文件无法解析：文件无法解析，请确认文件未损坏且格式为xlsx/xls后重新上传。
 列头不一致：模板列头【实际列名】与标准模板不一致，请下载最新模板修正后重新上传。
 缺少必填列：模板缺少必填列【列名】，请修正后重新上传。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="60" t="str">
+      <x:c r="A4" s="70" t="str">
         <x:v>基础必填缺失</x:v>
       </x:c>
-      <x:c r="B4" s="60" t="str">
+      <x:c r="B4" s="70" t="str">
         <x:v>导入规则配置为必填或条件必填的字段为空</x:v>
       </x:c>
-      <x:c r="C4" s="60" t="str">
+      <x:c r="C4" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D4" s="60" t="str">
+      <x:c r="D4" s="70" t="str">
         <x:v>续租订单违约日为空</x:v>
       </x:c>
-      <x:c r="E4" s="60" t="str">
+      <x:c r="E4" s="70" t="str">
         <x:v>【字段名】不能为空</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="60" t="str">
+      <x:c r="A5" s="70" t="str">
         <x:v>字段格式错误</x:v>
       </x:c>
-      <x:c r="B5" s="60" t="str">
+      <x:c r="B5" s="70" t="str">
         <x:v>身份证号、手机号、日期、枚举值等不符合字段校验规则</x:v>
       </x:c>
-      <x:c r="C5" s="60" t="str">
+      <x:c r="C5" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D5" s="60" t="str">
+      <x:c r="D5" s="70" t="str">
         <x:v>身份证号字段格式错误</x:v>
       </x:c>
-      <x:c r="E5" s="60" t="str">
+      <x:c r="E5" s="70" t="str">
         <x:v>【字段名】字段格式错误</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="60" t="str">
+      <x:c r="A6" s="70" t="str">
         <x:v>金额异常</x:v>
       </x:c>
-      <x:c r="B6" s="60" t="str">
+      <x:c r="B6" s="70" t="str">
         <x:v>金额非数字、负数，或金额关系不合法</x:v>
       </x:c>
-      <x:c r="C6" s="60" t="str">
+      <x:c r="C6" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D6" s="60" t="str">
+      <x:c r="D6" s="70" t="str">
         <x:v>债权金额异常</x:v>
       </x:c>
-      <x:c r="E6" s="60" t="str">
+      <x:c r="E6" s="70" t="str">
         <x:v>【字段名】金额异常</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="60" t="str">
+      <x:c r="A7" s="70" t="str">
         <x:v>首错输出规则</x:v>
       </x:c>
-      <x:c r="B7" s="60" t="str">
+      <x:c r="B7" s="70" t="str">
         <x:v>同一订单命中多个字段或多类校验问题时，仅输出按优先级命中的首个订单级失败原因</x:v>
       </x:c>
-      <x:c r="C7" s="60" t="str">
+      <x:c r="C7" s="70" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="D7" s="60" t="str">
+      <x:c r="D7" s="70" t="str">
         <x:v>基础必填缺失 → 字段格式错误 → 金额异常 → 主续关系异常 → 重复订单</x:v>
       </x:c>
-      <x:c r="E7" s="60" t="str">
+      <x:c r="E7" s="70" t="str">
         <x:v>仅展示按校验优先级命中的首个订单级失败原因</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="60" t="str">
+      <x:c r="A8" s="70" t="str">
         <x:v>主续关系异常</x:v>
       </x:c>
-      <x:c r="B8" s="60" t="str">
+      <x:c r="B8" s="70" t="str">
         <x:v>首次导入续租订单时主订单未同批导入、主订单不是已结清状态、父子证件号不一致；或主订单已作为初始订单导入后再次导入续租订单</x:v>
       </x:c>
-      <x:c r="C8" s="60" t="str">
+      <x:c r="C8" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D8" s="60" t="str">
+      <x:c r="D8" s="70" t="str">
         <x:v>主订单已作为初始订单导入后，再导入对应续租订单</x:v>
       </x:c>
-      <x:c r="E8" s="60" t="str">
+      <x:c r="E8" s="70" t="str">
         <x:v>未匹配到父订单：未匹配到父订单，请将已结清主订单与续租订单一并导入后重新上传。
 主订单非已结清：父订单不是已结清状态，不符合续租订单导入条件。
 证件号不一致：父订单客户证件号与当前订单身份证号不一致，请核对父订单编号和身份证号后重新上传。
@@ -2590,163 +2636,163 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="60" t="str">
+      <x:c r="A9" s="70" t="str">
         <x:v>重复订单</x:v>
       </x:c>
-      <x:c r="B9" s="60" t="str">
+      <x:c r="B9" s="70" t="str">
         <x:v>跨批次同一外部资产方+订单编号已存在；或同批次订单已分配/已流转，不可覆盖。</x:v>
       </x:c>
-      <x:c r="C9" s="60" t="str">
+      <x:c r="C9" s="70" t="str">
         <x:v>跨批次：是；同批次跳过：否</x:v>
       </x:c>
-      <x:c r="D9" s="60" t="str">
+      <x:c r="D9" s="70" t="str">
         <x:v>重复跳过</x:v>
       </x:c>
-      <x:c r="E9" s="60" t="str">
+      <x:c r="E9" s="70" t="str">
         <x:v>跨批次重复：导入结果=导入失败，失败分类=重复订单，处理结果为“该订单已在批次【批次号】导入，本次不允许重复导入”。
 同批次重复跳过：导入结果=导入成功，案件状态和材料状态保持当前最终状态；失败分类、失败字段和字段值为空，处理结果为“重复跳过：该订单已分配或已流转，不可覆盖”；本次失败另写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="60" t="str">
+      <x:c r="A10" s="70" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="B10" s="60" t="str">
+      <x:c r="B10" s="70" t="str">
         <x:v>订单字段校验通过，但材料包未匹配到导入规则要求的必填材料</x:v>
       </x:c>
-      <x:c r="C10" s="60" t="str">
+      <x:c r="C10" s="70" t="str">
         <x:v>不阻断导入；案件待材料激活</x:v>
       </x:c>
-      <x:c r="D10" s="60" t="str">
+      <x:c r="D10" s="70" t="str">
         <x:v>缺少租赁服务合同</x:v>
       </x:c>
-      <x:c r="E10" s="60" t="str">
+      <x:c r="E10" s="70" t="str">
         <x:v>缺少必填材料：{材料名称}；请通过批量补传仅上传材料包。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="60" t="str">
+      <x:c r="A11" s="70" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="B11" s="60" t="str">
+      <x:c r="B11" s="70" t="str">
         <x:v>订单字段校验通过，但材料包未匹配到导入规则要求的非必填材料</x:v>
       </x:c>
-      <x:c r="C11" s="60" t="str">
+      <x:c r="C11" s="70" t="str">
         <x:v>不阻断导入；案件保持已生效</x:v>
       </x:c>
-      <x:c r="D11" s="60" t="str">
+      <x:c r="D11" s="70" t="str">
         <x:v>缺少订单详情-物流</x:v>
       </x:c>
-      <x:c r="E11" s="60" t="str">
+      <x:c r="E11" s="70" t="str">
         <x:v>缺少非必填材料：{材料名称}；可按需通过批量补传仅上传材料包。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="62" t="str">
+      <x:c r="A12" s="72" t="str">
         <x:v>材料解析异常</x:v>
       </x:c>
-      <x:c r="B12" s="62" t="str">
+      <x:c r="B12" s="72" t="str">
         <x:v>材料包无法解压、文件无法识别订单归属或未匹配到材料规则</x:v>
       </x:c>
-      <x:c r="C12" s="62" t="str">
+      <x:c r="C12" s="72" t="str">
         <x:v>不阻断其它订单导入</x:v>
       </x:c>
-      <x:c r="D12" s="62" t="str">
+      <x:c r="D12" s="72" t="str">
         <x:v>订单编号无法匹配</x:v>
       </x:c>
-      <x:c r="E12" s="62" t="str">
+      <x:c r="E12" s="72" t="str">
         <x:v>材料文件未匹配到订单或材料规则，已进入异常文件清单。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="62" t="str">
+      <x:c r="A13" s="72" t="str">
         <x:v>失败文案规范</x:v>
       </x:c>
-      <x:c r="B13" s="62" t="str">
+      <x:c r="B13" s="72" t="str">
         <x:v>订单级字段格式与金额异常按统一格式输出，便于运营定位Excel列</x:v>
       </x:c>
-      <x:c r="C13" s="62" t="str">
+      <x:c r="C13" s="72" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="D13" s="62" t="str">
+      <x:c r="D13" s="72" t="str">
         <x:v>字段名+字段格式错误；字段名+金额异常</x:v>
       </x:c>
-      <x:c r="E13" s="62" t="str">
+      <x:c r="E13" s="72" t="str">
         <x:v>字段格式错误：字段名+字段格式错误；金额异常：字段名+金额异常</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="62" t="str">
+      <x:c r="A14" s="72" t="str">
         <x:v>系统异常</x:v>
       </x:c>
-      <x:c r="B14" s="62" t="str">
+      <x:c r="B14" s="72" t="str">
         <x:v>任务创建后，异步解析、校验或落库发生技术异常；按订单维度处理</x:v>
       </x:c>
-      <x:c r="C14" s="62" t="str">
+      <x:c r="C14" s="72" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D14" s="62" t="str">
+      <x:c r="D14" s="72" t="str">
         <x:v>提示“系统异常”；整批订单均导入失败时批次状态为导入失败，存在成功订单时批次状态为导入完成，导入结果明细按订单维度展示导入结果</x:v>
       </x:c>
-      <x:c r="E14" s="62" t="str">
+      <x:c r="E14" s="72" t="str">
         <x:v>系统异常</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="66" t="str">
+      <x:c r="A15" s="78" t="str">
         <x:v>覆盖成功口径</x:v>
       </x:c>
-      <x:c r="B15" s="66" t="str">
+      <x:c r="B15" s="78" t="str">
         <x:v>同批次订单未分配且未流转时自动覆盖。</x:v>
       </x:c>
-      <x:c r="C15" s="66" t="str">
+      <x:c r="C15" s="78" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D15" s="66" t="str">
+      <x:c r="D15" s="78" t="str">
         <x:v>同批次覆盖成功</x:v>
       </x:c>
-      <x:c r="E15" s="66" t="str">
+      <x:c r="E15" s="78" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；普通导入的处理结果为“成功”。同批次覆盖时，处理结果为“同批次覆盖成功：使用后传Excel字段覆盖已有订单”。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="66" t="str">
+      <x:c r="A16" s="78" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="B16" s="66" t="str">
+      <x:c r="B16" s="78" t="str">
         <x:v>本次同时导入主订单和续租订单，系统中已存在对应主子订单案件且均未流转。</x:v>
       </x:c>
-      <x:c r="C16" s="66" t="str">
+      <x:c r="C16" s="78" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="D16" s="66" t="str">
+      <x:c r="D16" s="78" t="str">
         <x:v>主子订单更新成功</x:v>
       </x:c>
-      <x:c r="E16" s="66" t="str">
+      <x:c r="E16" s="78" t="str">
         <x:v>导入结果=导入成功；案件状态=已生效、材料状态=材料齐全时，失败分类、失败字段和字段值为空；处理结果为“主子订单更新成功：主订单和续租订单均已存在且未流转，已按本次Excel更新”。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="67" t="str">
+      <x:c r="A17" s="79" t="str">
         <x:v>最终结果保留口径</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="str">
+      <x:c r="B17" s="79" t="str">
         <x:v>订单已为导入成功且待材料激活，后续再次上传Excel但本次字段校验失败。</x:v>
       </x:c>
-      <x:c r="C17" s="67" t="str">
+      <x:c r="C17" s="79" t="str">
         <x:v>本次记录失败；不覆盖订单最终结果</x:v>
       </x:c>
-      <x:c r="D17" s="67" t="str">
+      <x:c r="D17" s="79" t="str">
         <x:v>下载明细仍为导入成功 / 待材料激活 / 待补必填</x:v>
       </x:c>
-      <x:c r="E17" s="67" t="str">
+      <x:c r="E17" s="79" t="str">
         <x:v>本次Excel失败写入批次处理记录；下载明细按订单当前最终结果展示，处理结果保留当前缺失材料说明。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e480efee4cd4bf1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3273c9cb94e0416f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2772,196 +2818,196 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="60" t="str">
+      <x:c r="A2" s="70" t="str">
         <x:v>适用范围</x:v>
       </x:c>
-      <x:c r="B2" s="60" t="str">
+      <x:c r="B2" s="70" t="str">
         <x:v>本明细用于二期案件导入及一期历史批次补充材料后的结果排查。</x:v>
       </x:c>
-      <x:c r="C2" s="60" t="str">
+      <x:c r="C2" s="70" t="str">
         <x:v>一期已生效案件不回退；二期在原有案件基础上补齐材料处理能力。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
-      <x:c r="A3" s="60" t="str">
+      <x:c r="A3" s="70" t="str">
         <x:v>导入规则</x:v>
       </x:c>
-      <x:c r="B3" s="60" t="str">
+      <x:c r="B3" s="70" t="str">
         <x:v>导入字段、必填项和材料要求均以选中的导入规则为准。</x:v>
       </x:c>
-      <x:c r="C3" s="60" t="str">
+      <x:c r="C3" s="70" t="str">
         <x:v>前端可查看规则详情；规则配置由后台维护，订单字段与材料规则按资产方、业务类型生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="60" t="str">
+      <x:c r="A4" s="70" t="str">
         <x:v>Excel上传校验</x:v>
       </x:c>
-      <x:c r="B4" s="60" t="str">
+      <x:c r="B4" s="70" t="str">
         <x:v>列头须与模板一致，列顺序可调整，额外列忽略；同一文件内订单编号重复时整份文件上传失败。</x:v>
       </x:c>
-      <x:c r="C4" s="60" t="str">
+      <x:c r="C4" s="70" t="str">
         <x:v>列头不一致、缺少模板列、文件超限或单文件重复订单均在上传阶段拦截，不创建导入任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="60" t="str">
+      <x:c r="A5" s="70" t="str">
         <x:v>点击导入校验</x:v>
       </x:c>
-      <x:c r="B5" s="60" t="str">
+      <x:c r="B5" s="70" t="str">
         <x:v>订单必填字段为空、订单编号为空、格式或金额不合法等，按订单维度校验。</x:v>
       </x:c>
-      <x:c r="C5" s="60" t="str">
+      <x:c r="C5" s="70" t="str">
         <x:v>校验失败仅影响对应订单，其余订单继续处理；失败原因写入导入结果明细。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="60" t="str">
+      <x:c r="A6" s="70" t="str">
         <x:v>材料包上传</x:v>
       </x:c>
-      <x:c r="B6" s="60" t="str">
+      <x:c r="B6" s="70" t="str">
         <x:v>新建二期批次须同时上传Excel和材料包；材料包仅支持zip。</x:v>
       </x:c>
-      <x:c r="C6" s="60" t="str">
+      <x:c r="C6" s="70" t="str">
         <x:v>未上传材料包或上传非zip格式时整批不能提交；材料包解析异常不影响其它订单的字段处理。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="60" t="str">
+      <x:c r="A7" s="70" t="str">
         <x:v>草稿与批次状态</x:v>
       </x:c>
-      <x:c r="B7" s="60" t="str">
+      <x:c r="B7" s="70" t="str">
         <x:v>本期不提供保存草稿；未提交页面取消后不创建批次。</x:v>
       </x:c>
-      <x:c r="C7" s="60" t="str">
+      <x:c r="C7" s="70" t="str">
         <x:v>批次导入状态仅为导入中、导入完成、导入失败。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="60" t="str">
+      <x:c r="A8" s="70" t="str">
         <x:v>异步处理</x:v>
       </x:c>
-      <x:c r="B8" s="60" t="str">
+      <x:c r="B8" s="70" t="str">
         <x:v>点击导入后创建异步任务，页面展示“导入中”；任务结束后进入导入完成或导入失败。</x:v>
       </x:c>
-      <x:c r="C8" s="60" t="str">
+      <x:c r="C8" s="70" t="str">
         <x:v>确认提示后返回案件导入管理，可进入导入处理详情或下载明细查看处理结果。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="60" t="str">
+      <x:c r="A9" s="70" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="B9" s="60" t="str">
+      <x:c r="B9" s="70" t="str">
         <x:v>已生效：字段及必填材料均满足；待材料激活：字段通过但缺少必填材料；导入失败：订单字段或业务校验未通过。</x:v>
       </x:c>
-      <x:c r="C9" s="60" t="str">
+      <x:c r="C9" s="70" t="str">
         <x:v>待材料激活订单补齐必填材料并解析通过后自动变更为已生效。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="60" t="str">
+      <x:c r="A10" s="70" t="str">
         <x:v>材料状态</x:v>
       </x:c>
-      <x:c r="B10" s="60" t="str">
-        <x:v>材料齐全、待补必填、待补非必填、未生成四种状态；待补材料展示当前缺失材料名称。</x:v>
-      </x:c>
-      <x:c r="C10" s="60" t="str">
-        <x:v>缺少非必填材料不影响案件生效；材料异常文件在“异常文件”中查看。</x:v>
+      <x:c r="B10" s="70" t="str">
+        <x:v>未生成、材料齐全、待补必填、待补非必填四种状态；待补材料展示当前缺失材料名称。</x:v>
+      </x:c>
+      <x:c r="C10" s="70" t="str">
+        <x:v>一期未补材、字段失败或尚无解析结果为未生成；字段成功后先校验必填材料，再校验非必填材料。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="62" t="str">
+      <x:c r="A11" s="72" t="str">
         <x:v>批量补传</x:v>
       </x:c>
-      <x:c r="B11" s="62" t="str">
+      <x:c r="B11" s="72" t="str">
         <x:v>同一批次可分多次上传，每次订单Excel最多500条。</x:v>
       </x:c>
-      <x:c r="C11" s="62" t="str">
+      <x:c r="C11" s="72" t="str">
         <x:v>支持新增订单及材料、失败订单重新导入、仅补缺失材料、仅补订单Excel；处理过程归集在原批次。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="62" t="str">
+      <x:c r="A12" s="72" t="str">
         <x:v>最终结果导出</x:v>
       </x:c>
-      <x:c r="B12" s="62" t="str">
+      <x:c r="B12" s="72" t="str">
         <x:v>下载明细按订单当前最终结果导出，不按最后一次上传动作覆盖既有结果。</x:v>
       </x:c>
-      <x:c r="C12" s="62" t="str">
+      <x:c r="C12" s="72" t="str">
         <x:v>待材料激活订单后续Excel校验失败时，仍展示导入成功、待材料激活、待补必填；本次失败仅写入批次处理记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="62" t="str">
+      <x:c r="A13" s="72" t="str">
         <x:v>重复与覆盖</x:v>
       </x:c>
-      <x:c r="B13" s="62" t="str">
+      <x:c r="B13" s="72" t="str">
         <x:v>跨批次同一资产方订单不允许重复导入；同批次再次导入时按订单当前案件状态判断是否可覆盖。</x:v>
       </x:c>
-      <x:c r="C13" s="62" t="str">
+      <x:c r="C13" s="72" t="str">
         <x:v>案件已流转的订单不可覆盖；未流转且满足条件的订单可使用新上传Excel字段更新。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="62" t="str">
+      <x:c r="A14" s="72" t="str">
         <x:v>主续订单</x:v>
       </x:c>
-      <x:c r="B14" s="62" t="str">
+      <x:c r="B14" s="72" t="str">
         <x:v>首次导入续租订单时，主订单须同批导入且为已结清状态；首次导入主订单后，不允许再导入对应续租订单。</x:v>
       </x:c>
-      <x:c r="C14" s="62" t="str">
+      <x:c r="C14" s="72" t="str">
         <x:v>主子订单同批复导且案件均未流转时可更新；仅已有主订单或单独导入续租订单时按主续关系异常阻断。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="62" t="str">
+      <x:c r="A15" s="72" t="str">
         <x:v>历史批次补材</x:v>
       </x:c>
-      <x:c r="B15" s="62" t="str">
-        <x:v>一期历史案件仅导入Excel，案件已生效；材料状态初始为待初始化（一期）。</x:v>
-      </x:c>
-      <x:c r="C15" s="62" t="str">
-        <x:v>可通过补充历史材料上传ZIP材料包；解析后更新材料状态，不影响待委外及后续法诉流程。</x:v>
+      <x:c r="B15" s="72" t="str">
+        <x:v>一期历史案件仅导入Excel，案件已生效；未补充材料时材料状态为未生成。</x:v>
+      </x:c>
+      <x:c r="C15" s="72" t="str">
+        <x:v>提交ZIP材料包后材料状态保持未生成，批次处理记录显示处理中；解析完成后更新为材料齐全、待补必填或待补非必填。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="62" t="str">
+      <x:c r="A16" s="72" t="str">
         <x:v>下载明细</x:v>
       </x:c>
-      <x:c r="B16" s="62" t="str">
+      <x:c r="B16" s="72" t="str">
         <x:v>批次管理“下载明细”与导入处理详情“导出当前筛选订单明细”使用同一模板。</x:v>
       </x:c>
-      <x:c r="C16" s="62" t="str">
+      <x:c r="C16" s="72" t="str">
         <x:v>工作簿包含导入结果明细、待补材料明细、失败分类说明、口径说明。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="62" t="str">
+      <x:c r="A17" s="72" t="str">
         <x:v>法诉材料导出</x:v>
       </x:c>
-      <x:c r="B17" s="62" t="str">
+      <x:c r="B17" s="72" t="str">
         <x:v>一期历史案件在未补齐材料前不支持导出法诉材料。</x:v>
       </x:c>
-      <x:c r="C17" s="62" t="str">
+      <x:c r="C17" s="72" t="str">
         <x:v>历史案件补充材料包且解析完成后，可在法诉系统现有功能中按既有能力导出法诉材料。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="62" t="str">
+      <x:c r="A18" s="72" t="str">
         <x:v>批次信息与附件</x:v>
       </x:c>
-      <x:c r="B18" s="62" t="str">
+      <x:c r="B18" s="72" t="str">
         <x:v>债权出让主体为文本输入，最多50字；附件用于留存债权转让协议、转账回单、补充协议等。</x:v>
       </x:c>
-      <x:c r="C18" s="62" t="str">
+      <x:c r="C18" s="72" t="str">
         <x:v>单批次最多10个附件，支持pdf、图片、xlsx、xls、zip；已上传附件支持下载、删除。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra92383a111154567"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fcec2c0b8eb4d49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2982,212 +3028,212 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="65" t="str">
+      <x:c r="A1" s="75" t="str">
         <x:v>订单编号</x:v>
       </x:c>
-      <x:c r="B1" s="65" t="str">
+      <x:c r="B1" s="75" t="str">
         <x:v>客户姓名</x:v>
       </x:c>
-      <x:c r="C1" s="65" t="str">
+      <x:c r="C1" s="75" t="str">
         <x:v>标准材料类别</x:v>
       </x:c>
-      <x:c r="D1" s="65" t="str">
+      <x:c r="D1" s="75" t="str">
         <x:v>缺失材料名称</x:v>
       </x:c>
-      <x:c r="E1" s="65" t="str">
+      <x:c r="E1" s="75" t="str">
         <x:v>材料要求</x:v>
       </x:c>
-      <x:c r="F1" s="65" t="str">
+      <x:c r="F1" s="75" t="str">
         <x:v>案件状态</x:v>
       </x:c>
-      <x:c r="G1" s="65" t="str">
+      <x:c r="G1" s="75" t="str">
         <x:v>处理结果</x:v>
       </x:c>
-      <x:c r="H1" s="65" t="str">
+      <x:c r="H1" s="75" t="str">
         <x:v>导入时间</x:v>
       </x:c>
-      <x:c r="I1" s="65" t="str">
+      <x:c r="I1" s="75" t="str">
         <x:v>业务主体1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="63" t="str">
+      <x:c r="A2" s="73" t="str">
         <x:v>26012915050167612342</x:v>
       </x:c>
-      <x:c r="B2" s="62" t="str">
+      <x:c r="B2" s="72" t="str">
         <x:v>孙悦</x:v>
       </x:c>
-      <x:c r="C2" s="62" t="str">
+      <x:c r="C2" s="72" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D2" s="62" t="str">
+      <x:c r="D2" s="72" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E2" s="62" t="str">
+      <x:c r="E2" s="72" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F2" s="62" t="str">
+      <x:c r="F2" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G2" s="62" t="str">
+      <x:c r="G2" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H2" s="62" t="str">
+      <x:c r="H2" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="I2" s="62" t="str">
+      <x:c r="I2" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="63" t="str">
+      <x:c r="A3" s="73" t="str">
         <x:v>26012915050167612343</x:v>
       </x:c>
-      <x:c r="B3" s="62" t="str">
+      <x:c r="B3" s="72" t="str">
         <x:v>林浩</x:v>
       </x:c>
-      <x:c r="C3" s="62" t="str">
+      <x:c r="C3" s="72" t="str">
         <x:v>订单信息</x:v>
       </x:c>
-      <x:c r="D3" s="62" t="str">
+      <x:c r="D3" s="72" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="E3" s="62" t="str">
+      <x:c r="E3" s="72" t="str">
         <x:v>非必填</x:v>
       </x:c>
-      <x:c r="F3" s="62" t="str">
+      <x:c r="F3" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="G3" s="62" t="str">
+      <x:c r="G3" s="72" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="H3" s="62" t="str">
+      <x:c r="H3" s="72" t="str">
         <x:v>2026-06-12 09:20:16</x:v>
       </x:c>
-      <x:c r="I3" s="62" t="str">
+      <x:c r="I3" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="63" t="str">
+      <x:c r="A4" s="73" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B4" s="62" t="str">
+      <x:c r="B4" s="72" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C4" s="62" t="str">
+      <x:c r="C4" s="72" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D4" s="62" t="str">
+      <x:c r="D4" s="72" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E4" s="62" t="str">
+      <x:c r="E4" s="72" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F4" s="62" t="str">
+      <x:c r="F4" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G4" s="62" t="str">
+      <x:c r="G4" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H4" s="62" t="str">
+      <x:c r="H4" s="72" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I4" s="62" t="str">
+      <x:c r="I4" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="63" t="str">
+      <x:c r="A5" s="73" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B5" s="62" t="str">
+      <x:c r="B5" s="72" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C5" s="62" t="str">
+      <x:c r="C5" s="72" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D5" s="62" t="str">
+      <x:c r="D5" s="72" t="str">
         <x:v>租赁服务合同验签报告</x:v>
       </x:c>
-      <x:c r="E5" s="62" t="str">
+      <x:c r="E5" s="72" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F5" s="62" t="str">
+      <x:c r="F5" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G5" s="62" t="str">
+      <x:c r="G5" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H5" s="62" t="str">
+      <x:c r="H5" s="72" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I5" s="62" t="str">
+      <x:c r="I5" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="63" t="str">
+      <x:c r="A6" s="73" t="str">
         <x:v>26012915050167612348</x:v>
       </x:c>
-      <x:c r="B6" s="62" t="str">
+      <x:c r="B6" s="72" t="str">
         <x:v>丁磊</x:v>
       </x:c>
-      <x:c r="C6" s="62" t="str">
+      <x:c r="C6" s="72" t="str">
         <x:v>订单信息</x:v>
       </x:c>
-      <x:c r="D6" s="62" t="str">
+      <x:c r="D6" s="72" t="str">
         <x:v>订单详情-物流</x:v>
       </x:c>
-      <x:c r="E6" s="62" t="str">
+      <x:c r="E6" s="72" t="str">
         <x:v>非必填</x:v>
       </x:c>
-      <x:c r="F6" s="62" t="str">
+      <x:c r="F6" s="72" t="str">
         <x:v>待材料激活</x:v>
       </x:c>
-      <x:c r="G6" s="62" t="str">
+      <x:c r="G6" s="72" t="str">
         <x:v>缺少非必填材料</x:v>
       </x:c>
-      <x:c r="H6" s="62" t="str">
+      <x:c r="H6" s="72" t="str">
         <x:v>2026-06-12 10:12:08</x:v>
       </x:c>
-      <x:c r="I6" s="62" t="str">
+      <x:c r="I6" s="72" t="str">
         <x:v>雅安欣天下办公设备租赁有限公司</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="63" t="str">
+      <x:c r="A7" s="73" t="str">
         <x:v>26012915050167612001</x:v>
       </x:c>
-      <x:c r="B7" s="62" t="str">
+      <x:c r="B7" s="72" t="str">
         <x:v>吴静</x:v>
       </x:c>
-      <x:c r="C7" s="62" t="str">
+      <x:c r="C7" s="72" t="str">
         <x:v>主合同</x:v>
       </x:c>
-      <x:c r="D7" s="62" t="str">
+      <x:c r="D7" s="72" t="str">
         <x:v>租赁服务合同</x:v>
       </x:c>
-      <x:c r="E7" s="62" t="str">
+      <x:c r="E7" s="72" t="str">
         <x:v>必填</x:v>
       </x:c>
-      <x:c r="F7" s="62" t="str">
+      <x:c r="F7" s="72" t="str">
         <x:v>已生效</x:v>
       </x:c>
-      <x:c r="G7" s="62" t="str">
+      <x:c r="G7" s="72" t="str">
         <x:v>缺少必填材料</x:v>
       </x:c>
-      <x:c r="H7" s="62" t="str">
+      <x:c r="H7" s="72" t="str">
         <x:v>2026-06-12 10:15:26</x:v>
       </x:c>
-      <x:c r="I7" s="62" t="str">
+      <x:c r="I7" s="72" t="str">
         <x:v>雅安青年优品电子商务有限公司</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78f86adacd44478c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra800815e6a4d4d21"/>
   </x:tableParts>
 </x:worksheet>
 </file>